--- a/research/traditional_assets/database/data/israel/israel_retail_building_supply.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_retail_building_supply.xlsx
@@ -1260,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1397,22 +1397,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1074041575484147</v>
+        <v>0.1071917779860534</v>
       </c>
       <c r="C2">
-        <v>202.6972789450944</v>
+        <v>201.2618744637388</v>
       </c>
       <c r="D2">
-        <v>201.5072789450944</v>
+        <v>202.1608744637388</v>
       </c>
       <c r="E2">
-        <v>-125.2</v>
+        <v>-123.111</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.089</v>
       </c>
       <c r="G2">
         <v>1.19</v>
@@ -1433,28 +1433,28 @@
         <v>23.225</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1050767</v>
       </c>
       <c r="N2">
-        <v>23.225</v>
+        <v>23.1199233</v>
       </c>
       <c r="O2">
-        <v>5.341749999999999</v>
+        <v>5.317582358999999</v>
       </c>
       <c r="P2">
-        <v>17.88325</v>
+        <v>17.802340941</v>
       </c>
       <c r="Q2">
-        <v>21.78325</v>
+        <v>21.702340941</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1074041575484147</v>
+        <v>0.1078833009960135</v>
       </c>
       <c r="T2">
-        <v>0.9529967248041119</v>
+        <v>0.9604089215525884</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>221.0290197541415</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1479,22 +1479,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1071917779860534</v>
+        <v>0.106979398423692</v>
       </c>
       <c r="C3">
-        <v>201.2618744637388</v>
+        <v>199.8307236967758</v>
       </c>
       <c r="D3">
-        <v>202.1608744637388</v>
+        <v>202.8187236967758</v>
       </c>
       <c r="E3">
-        <v>-123.111</v>
+        <v>-121.022</v>
       </c>
       <c r="F3">
-        <v>2.089</v>
+        <v>4.178</v>
       </c>
       <c r="G3">
         <v>1.19</v>
@@ -1515,28 +1515,28 @@
         <v>23.225</v>
       </c>
       <c r="M3">
-        <v>0.1050767</v>
+        <v>0.2101534</v>
       </c>
       <c r="N3">
-        <v>23.1199233</v>
+        <v>23.0148466</v>
       </c>
       <c r="O3">
-        <v>5.317582358999999</v>
+        <v>5.293414718</v>
       </c>
       <c r="P3">
-        <v>17.802340941</v>
+        <v>17.721431882</v>
       </c>
       <c r="Q3">
-        <v>21.702340941</v>
+        <v>21.621431882</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1078833009960135</v>
+        <v>0.1083722228813184</v>
       </c>
       <c r="T3">
-        <v>0.9604089215525884</v>
+        <v>0.9679723876224623</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>221.0290197541415</v>
+        <v>110.5145098770708</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.106979398423692</v>
+        <v>0.1067670188613307</v>
       </c>
       <c r="C4">
-        <v>199.8307236967758</v>
+        <v>198.4038683056554</v>
       </c>
       <c r="D4">
-        <v>202.8187236967758</v>
+        <v>203.4808683056554</v>
       </c>
       <c r="E4">
-        <v>-121.022</v>
+        <v>-118.933</v>
       </c>
       <c r="F4">
-        <v>4.178</v>
+        <v>6.267</v>
       </c>
       <c r="G4">
         <v>1.19</v>
@@ -1597,28 +1597,28 @@
         <v>23.225</v>
       </c>
       <c r="M4">
-        <v>0.2101534</v>
+        <v>0.3152301</v>
       </c>
       <c r="N4">
-        <v>23.0148466</v>
+        <v>22.9097699</v>
       </c>
       <c r="O4">
-        <v>5.293414718</v>
+        <v>5.269247076999999</v>
       </c>
       <c r="P4">
-        <v>17.721431882</v>
+        <v>17.640522823</v>
       </c>
       <c r="Q4">
-        <v>21.621431882</v>
+        <v>21.540522823</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1083722228813184</v>
+        <v>0.1088712256302378</v>
       </c>
       <c r="T4">
-        <v>0.9679723876224623</v>
+        <v>0.9756918014463543</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>110.5145098770708</v>
+        <v>73.67633991804715</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1643,22 +1643,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1067670188613307</v>
+        <v>0.1065546392989693</v>
       </c>
       <c r="C5">
-        <v>198.4038683056554</v>
+        <v>196.9813504976606</v>
       </c>
       <c r="D5">
-        <v>203.4808683056554</v>
+        <v>204.1473504976606</v>
       </c>
       <c r="E5">
-        <v>-118.933</v>
+        <v>-116.844</v>
       </c>
       <c r="F5">
-        <v>6.267</v>
+        <v>8.356</v>
       </c>
       <c r="G5">
         <v>1.19</v>
@@ -1679,28 +1679,28 @@
         <v>23.225</v>
       </c>
       <c r="M5">
-        <v>0.3152301</v>
+        <v>0.4203068</v>
       </c>
       <c r="N5">
-        <v>22.9097699</v>
+        <v>22.8046932</v>
       </c>
       <c r="O5">
-        <v>5.269247076999999</v>
+        <v>5.245079436</v>
       </c>
       <c r="P5">
-        <v>17.640522823</v>
+        <v>17.559613764</v>
       </c>
       <c r="Q5">
-        <v>21.540522823</v>
+        <v>21.459613764</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1088712256302378</v>
+        <v>0.1093806242697597</v>
       </c>
       <c r="T5">
-        <v>0.9756918014463543</v>
+        <v>0.9835720363915771</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>73.67633991804715</v>
+        <v>55.25725493853538</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1725,22 +1725,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1065546392989693</v>
+        <v>0.1063422597366079</v>
       </c>
       <c r="C6">
-        <v>196.9813504976606</v>
+        <v>195.5632130348747</v>
       </c>
       <c r="D6">
-        <v>204.1473504976606</v>
+        <v>204.8182130348747</v>
       </c>
       <c r="E6">
-        <v>-116.844</v>
+        <v>-114.755</v>
       </c>
       <c r="F6">
-        <v>8.356</v>
+        <v>10.445</v>
       </c>
       <c r="G6">
         <v>1.19</v>
@@ -1761,28 +1761,28 @@
         <v>23.225</v>
       </c>
       <c r="M6">
-        <v>0.4203068</v>
+        <v>0.5253835</v>
       </c>
       <c r="N6">
-        <v>22.8046932</v>
+        <v>22.6996165</v>
       </c>
       <c r="O6">
-        <v>5.245079436</v>
+        <v>5.220911794999999</v>
       </c>
       <c r="P6">
-        <v>17.559613764</v>
+        <v>17.478704705</v>
       </c>
       <c r="Q6">
-        <v>21.459613764</v>
+        <v>21.378704705</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1093806242697597</v>
+        <v>0.1099007470911662</v>
       </c>
       <c r="T6">
-        <v>0.9835720363915771</v>
+        <v>0.9916181710198575</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>55.25725493853538</v>
+        <v>44.2058039508283</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1807,22 +1807,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1063422597366079</v>
+        <v>0.1061298801742466</v>
       </c>
       <c r="C7">
-        <v>195.5632130348747</v>
+        <v>194.149499243328</v>
       </c>
       <c r="D7">
-        <v>204.8182130348747</v>
+        <v>205.493499243328</v>
       </c>
       <c r="E7">
-        <v>-114.755</v>
+        <v>-112.666</v>
       </c>
       <c r="F7">
-        <v>10.445</v>
+        <v>12.534</v>
       </c>
       <c r="G7">
         <v>1.19</v>
@@ -1843,28 +1843,28 @@
         <v>23.225</v>
       </c>
       <c r="M7">
-        <v>0.5253835</v>
+        <v>0.6304602</v>
       </c>
       <c r="N7">
-        <v>22.6996165</v>
+        <v>22.5945398</v>
       </c>
       <c r="O7">
-        <v>5.220911794999999</v>
+        <v>5.196744153999999</v>
       </c>
       <c r="P7">
-        <v>17.478704705</v>
+        <v>17.397795646</v>
       </c>
       <c r="Q7">
-        <v>21.378704705</v>
+        <v>21.297795646</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1099007470911662</v>
+        <v>0.1104319363555815</v>
       </c>
       <c r="T7">
-        <v>0.9916181710198575</v>
+        <v>0.9998355000019311</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>44.2058039508283</v>
+        <v>36.83816995902357</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1889,22 +1889,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1061298801742466</v>
+        <v>0.1059175006118852</v>
       </c>
       <c r="C8">
-        <v>194.149499243328</v>
+        <v>192.7402530223254</v>
       </c>
       <c r="D8">
-        <v>205.493499243328</v>
+        <v>206.1732530223254</v>
       </c>
       <c r="E8">
-        <v>-112.666</v>
+        <v>-110.577</v>
       </c>
       <c r="F8">
-        <v>12.534</v>
+        <v>14.623</v>
       </c>
       <c r="G8">
         <v>1.19</v>
@@ -1925,28 +1925,28 @@
         <v>23.225</v>
       </c>
       <c r="M8">
-        <v>0.6304602</v>
+        <v>0.7355368999999999</v>
       </c>
       <c r="N8">
-        <v>22.5945398</v>
+        <v>22.4894631</v>
       </c>
       <c r="O8">
-        <v>5.196744153999999</v>
+        <v>5.172576513</v>
       </c>
       <c r="P8">
-        <v>17.397795646</v>
+        <v>17.316886587</v>
       </c>
       <c r="Q8">
-        <v>21.297795646</v>
+        <v>21.216886587</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1104319363555815</v>
+        <v>0.1109745490450379</v>
       </c>
       <c r="T8">
-        <v>0.9998355000019309</v>
+        <v>1.008229545736307</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>36.83816995902357</v>
+        <v>31.57557425059164</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1971,22 +1971,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1059175006118852</v>
+        <v>0.1057051210495239</v>
       </c>
       <c r="C9">
-        <v>192.7402530223254</v>
+        <v>191.3355188539588</v>
       </c>
       <c r="D9">
-        <v>206.1732530223254</v>
+        <v>206.8575188539588</v>
       </c>
       <c r="E9">
-        <v>-110.577</v>
+        <v>-108.488</v>
       </c>
       <c r="F9">
-        <v>14.623</v>
+        <v>16.712</v>
       </c>
       <c r="G9">
         <v>1.19</v>
@@ -2007,28 +2007,28 @@
         <v>23.225</v>
       </c>
       <c r="M9">
-        <v>0.7355369</v>
+        <v>0.8406136</v>
       </c>
       <c r="N9">
-        <v>22.4894631</v>
+        <v>22.3843864</v>
       </c>
       <c r="O9">
-        <v>5.172576513</v>
+        <v>5.148408871999999</v>
       </c>
       <c r="P9">
-        <v>17.316886587</v>
+        <v>17.235977528</v>
       </c>
       <c r="Q9">
-        <v>21.216886587</v>
+        <v>21.135977528</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1109745490450379</v>
+        <v>0.1115289576625259</v>
       </c>
       <c r="T9">
-        <v>1.008229545736307</v>
+        <v>1.016806070725778</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>31.57557425059164</v>
+        <v>27.62862746926768</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2053,22 +2053,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1057051210495239</v>
+        <v>0.1054927414871625</v>
       </c>
       <c r="C10">
-        <v>191.3355188539588</v>
+        <v>189.9353418128109</v>
       </c>
       <c r="D10">
-        <v>206.8575188539588</v>
+        <v>207.5463418128109</v>
       </c>
       <c r="E10">
-        <v>-108.488</v>
+        <v>-106.399</v>
       </c>
       <c r="F10">
-        <v>16.712</v>
+        <v>18.801</v>
       </c>
       <c r="G10">
         <v>1.19</v>
@@ -2089,28 +2089,28 @@
         <v>23.225</v>
       </c>
       <c r="M10">
-        <v>0.8406136</v>
+        <v>0.9456902999999999</v>
       </c>
       <c r="N10">
-        <v>22.3843864</v>
+        <v>22.2793097</v>
       </c>
       <c r="O10">
-        <v>5.148408871999999</v>
+        <v>5.124241231</v>
       </c>
       <c r="P10">
-        <v>17.235977528</v>
+        <v>17.155068469</v>
       </c>
       <c r="Q10">
-        <v>21.135977528</v>
+        <v>21.055068469</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1115289576625259</v>
+        <v>0.112095551084794</v>
       </c>
       <c r="T10">
-        <v>1.016806070725778</v>
+        <v>1.025571090769964</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>27.62862746926768</v>
+        <v>24.55877997268239</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2135,22 +2135,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1054927414871625</v>
+        <v>0.1052803619248012</v>
       </c>
       <c r="C11">
-        <v>189.9353418128109</v>
+        <v>188.539767575853</v>
       </c>
       <c r="D11">
-        <v>207.5463418128109</v>
+        <v>208.239767575853</v>
       </c>
       <c r="E11">
-        <v>-106.399</v>
+        <v>-104.31</v>
       </c>
       <c r="F11">
-        <v>18.801</v>
+        <v>20.89</v>
       </c>
       <c r="G11">
         <v>1.19</v>
@@ -2171,28 +2171,28 @@
         <v>23.225</v>
       </c>
       <c r="M11">
-        <v>0.9456902999999999</v>
+        <v>1.050767</v>
       </c>
       <c r="N11">
-        <v>22.2793097</v>
+        <v>22.174233</v>
       </c>
       <c r="O11">
-        <v>5.124241231</v>
+        <v>5.10007359</v>
       </c>
       <c r="P11">
-        <v>17.155068469</v>
+        <v>17.07415941</v>
       </c>
       <c r="Q11">
-        <v>21.055068469</v>
+        <v>20.97415941</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.112095551084794</v>
+        <v>0.1126747354720013</v>
       </c>
       <c r="T11">
-        <v>1.025571090769964</v>
+        <v>1.034530889037353</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>24.55877997268239</v>
+        <v>22.10290197541415</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2217,22 +2217,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1052803619248012</v>
+        <v>0.1050679823624398</v>
       </c>
       <c r="C12">
-        <v>188.539767575853</v>
+        <v>187.1488424325412</v>
       </c>
       <c r="D12">
-        <v>208.239767575853</v>
+        <v>208.9378424325412</v>
       </c>
       <c r="E12">
-        <v>-104.31</v>
+        <v>-102.221</v>
       </c>
       <c r="F12">
-        <v>20.89</v>
+        <v>22.979</v>
       </c>
       <c r="G12">
         <v>1.19</v>
@@ -2253,28 +2253,28 @@
         <v>23.225</v>
       </c>
       <c r="M12">
-        <v>1.050767</v>
+        <v>1.1558437</v>
       </c>
       <c r="N12">
-        <v>22.174233</v>
+        <v>22.0691563</v>
       </c>
       <c r="O12">
-        <v>5.10007359</v>
+        <v>5.075905949</v>
       </c>
       <c r="P12">
-        <v>17.07415941</v>
+        <v>16.993250351</v>
       </c>
       <c r="Q12">
-        <v>20.97415941</v>
+        <v>20.893250351</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1126747354720013</v>
+        <v>0.1132669352386964</v>
       </c>
       <c r="T12">
-        <v>1.034530889037353</v>
+        <v>1.043692031086031</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.10290197541415</v>
+        <v>20.0935472503765</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2299,22 +2299,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1050679823624398</v>
+        <v>0.1048556028000785</v>
       </c>
       <c r="C13">
-        <v>187.1488424325412</v>
+        <v>185.7626132951177</v>
       </c>
       <c r="D13">
-        <v>208.9378424325412</v>
+        <v>209.6406132951178</v>
       </c>
       <c r="E13">
-        <v>-102.221</v>
+        <v>-100.132</v>
       </c>
       <c r="F13">
-        <v>22.979</v>
+        <v>25.068</v>
       </c>
       <c r="G13">
         <v>1.19</v>
@@ -2335,28 +2335,28 @@
         <v>23.225</v>
       </c>
       <c r="M13">
-        <v>1.1558437</v>
+        <v>1.2609204</v>
       </c>
       <c r="N13">
-        <v>22.0691563</v>
+        <v>21.9640796</v>
       </c>
       <c r="O13">
-        <v>5.075905949</v>
+        <v>5.051738308</v>
       </c>
       <c r="P13">
-        <v>16.993250351</v>
+        <v>16.912341292</v>
       </c>
       <c r="Q13">
-        <v>20.893250351</v>
+        <v>20.812341292</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1132669352386964</v>
+        <v>0.1138725940909983</v>
       </c>
       <c r="T13">
-        <v>1.043692031086031</v>
+        <v>1.053061380908544</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.0935472503765</v>
+        <v>18.41908497951179</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2381,22 +2381,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1048556028000785</v>
+        <v>0.1046432232377171</v>
       </c>
       <c r="C14">
-        <v>185.7626132951177</v>
+        <v>184.3811277091198</v>
       </c>
       <c r="D14">
-        <v>209.6406132951178</v>
+        <v>210.3481277091198</v>
       </c>
       <c r="E14">
-        <v>-100.132</v>
+        <v>-98.04300000000001</v>
       </c>
       <c r="F14">
-        <v>25.068</v>
+        <v>27.157</v>
       </c>
       <c r="G14">
         <v>1.19</v>
@@ -2417,28 +2417,28 @@
         <v>23.225</v>
       </c>
       <c r="M14">
-        <v>1.2609204</v>
+        <v>1.3659971</v>
       </c>
       <c r="N14">
-        <v>21.9640796</v>
+        <v>21.8590029</v>
       </c>
       <c r="O14">
-        <v>5.051738308</v>
+        <v>5.027570666999999</v>
       </c>
       <c r="P14">
-        <v>16.912341292</v>
+        <v>16.831432233</v>
       </c>
       <c r="Q14">
-        <v>20.812341292</v>
+        <v>20.731432233</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1138725940909983</v>
+        <v>0.114492176135307</v>
       </c>
       <c r="T14">
-        <v>1.053061380908544</v>
+        <v>1.062646118083298</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.41908497951179</v>
+        <v>17.00223228878011</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2463,22 +2463,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1046432232377171</v>
+        <v>0.1044308436753558</v>
       </c>
       <c r="C15">
-        <v>184.3811277091198</v>
+        <v>183.004433864102</v>
       </c>
       <c r="D15">
-        <v>210.3481277091198</v>
+        <v>211.060433864102</v>
       </c>
       <c r="E15">
-        <v>-98.04300000000001</v>
+        <v>-95.95400000000001</v>
       </c>
       <c r="F15">
-        <v>27.157</v>
+        <v>29.246</v>
       </c>
       <c r="G15">
         <v>1.19</v>
@@ -2499,28 +2499,28 @@
         <v>23.225</v>
       </c>
       <c r="M15">
-        <v>1.3659971</v>
+        <v>1.4710738</v>
       </c>
       <c r="N15">
-        <v>21.8590029</v>
+        <v>21.7539262</v>
       </c>
       <c r="O15">
-        <v>5.027570666999999</v>
+        <v>5.003403026</v>
       </c>
       <c r="P15">
-        <v>16.831432233</v>
+        <v>16.750523174</v>
       </c>
       <c r="Q15">
-        <v>20.731432233</v>
+        <v>20.650523174</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.114492176135307</v>
+        <v>0.1151261670643672</v>
       </c>
       <c r="T15">
-        <v>1.062646118083298</v>
+        <v>1.072453756122581</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.00223228878011</v>
+        <v>15.78778712529582</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2545,22 +2545,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1044308436753558</v>
+        <v>0.1042184641129944</v>
       </c>
       <c r="C16">
-        <v>183.004433864102</v>
+        <v>181.6325806045784</v>
       </c>
       <c r="D16">
-        <v>211.060433864102</v>
+        <v>211.7775806045784</v>
       </c>
       <c r="E16">
-        <v>-95.95400000000001</v>
+        <v>-93.86499999999999</v>
       </c>
       <c r="F16">
-        <v>29.246</v>
+        <v>31.335</v>
       </c>
       <c r="G16">
         <v>1.19</v>
@@ -2581,28 +2581,28 @@
         <v>23.225</v>
       </c>
       <c r="M16">
-        <v>1.4710738</v>
+        <v>1.5761505</v>
       </c>
       <c r="N16">
-        <v>21.7539262</v>
+        <v>21.6488495</v>
       </c>
       <c r="O16">
-        <v>5.003403026</v>
+        <v>4.979235385</v>
       </c>
       <c r="P16">
-        <v>16.750523174</v>
+        <v>16.669614115</v>
       </c>
       <c r="Q16">
-        <v>20.650523174</v>
+        <v>20.569614115</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1151261670643672</v>
+        <v>0.1157750754270522</v>
       </c>
       <c r="T16">
-        <v>1.072453756122581</v>
+        <v>1.08249216211573</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.78778712529582</v>
+        <v>14.73526798360943</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1042184641129944</v>
+        <v>0.1040060845506331</v>
       </c>
       <c r="C17">
-        <v>181.6325806045784</v>
+        <v>180.2656174411866</v>
       </c>
       <c r="D17">
-        <v>211.7775806045784</v>
+        <v>212.4996174411866</v>
       </c>
       <c r="E17">
-        <v>-93.86500000000001</v>
+        <v>-91.77600000000001</v>
       </c>
       <c r="F17">
-        <v>31.335</v>
+        <v>33.424</v>
       </c>
       <c r="G17">
         <v>1.19</v>
@@ -2663,28 +2663,28 @@
         <v>23.225</v>
       </c>
       <c r="M17">
-        <v>1.5761505</v>
+        <v>1.6812272</v>
       </c>
       <c r="N17">
-        <v>21.6488495</v>
+        <v>21.5437728</v>
       </c>
       <c r="O17">
-        <v>4.979235385</v>
+        <v>4.955067744</v>
       </c>
       <c r="P17">
-        <v>16.669614115</v>
+        <v>16.588705056</v>
       </c>
       <c r="Q17">
-        <v>20.569614115</v>
+        <v>20.488705056</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1157750754270522</v>
+        <v>0.1164394339888489</v>
       </c>
       <c r="T17">
-        <v>1.08249216211573</v>
+        <v>1.092769577775382</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.73526798360943</v>
+        <v>13.81431373463384</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2709,22 +2709,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1040060845506331</v>
+        <v>0.1037937049882717</v>
       </c>
       <c r="C18">
-        <v>180.2656174411866</v>
+        <v>178.9035945620832</v>
       </c>
       <c r="D18">
-        <v>212.4996174411866</v>
+        <v>213.2265945620832</v>
       </c>
       <c r="E18">
-        <v>-91.77600000000001</v>
+        <v>-89.687</v>
       </c>
       <c r="F18">
-        <v>33.424</v>
+        <v>35.51300000000001</v>
       </c>
       <c r="G18">
         <v>1.19</v>
@@ -2745,28 +2745,28 @@
         <v>23.225</v>
       </c>
       <c r="M18">
-        <v>1.6812272</v>
+        <v>1.7863039</v>
       </c>
       <c r="N18">
-        <v>21.5437728</v>
+        <v>21.4386961</v>
       </c>
       <c r="O18">
-        <v>4.955067744</v>
+        <v>4.930900103</v>
       </c>
       <c r="P18">
-        <v>16.588705056</v>
+        <v>16.507795997</v>
       </c>
       <c r="Q18">
-        <v>20.488705056</v>
+        <v>20.407795997</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1164394339888489</v>
+        <v>0.1171198011906888</v>
       </c>
       <c r="T18">
-        <v>1.092769577775382</v>
+        <v>1.103294642005146</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>13.81431373463384</v>
+        <v>13.00170704436126</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2791,22 +2791,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1037937049882717</v>
+        <v>0.1037892254259103</v>
       </c>
       <c r="C19">
-        <v>178.9035945620832</v>
+        <v>176.8299817113176</v>
       </c>
       <c r="D19">
-        <v>213.2265945620832</v>
+        <v>213.2419817113176</v>
       </c>
       <c r="E19">
-        <v>-89.687</v>
+        <v>-87.598</v>
       </c>
       <c r="F19">
-        <v>35.51300000000001</v>
+        <v>37.602</v>
       </c>
       <c r="G19">
         <v>1.19</v>
@@ -2827,45 +2827,45 @@
         <v>23.225</v>
       </c>
       <c r="M19">
-        <v>1.7863039</v>
+        <v>1.9477836</v>
       </c>
       <c r="N19">
-        <v>21.4386961</v>
+        <v>21.2772164</v>
       </c>
       <c r="O19">
-        <v>4.930900103</v>
+        <v>4.893759771999999</v>
       </c>
       <c r="P19">
-        <v>16.507795997</v>
+        <v>16.383456628</v>
       </c>
       <c r="Q19">
-        <v>20.407795997</v>
+        <v>20.283456628</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1171198011906888</v>
+        <v>0.1178167627145248</v>
       </c>
       <c r="T19">
-        <v>1.103294642005146</v>
+        <v>1.114076415118563</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.23</v>
       </c>
       <c r="W19">
-        <v>0.038731</v>
+        <v>0.039886</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>13.00170704436126</v>
+        <v>11.92380919523093</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2873,22 +2873,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1037892254259103</v>
+        <v>0.103588395863549</v>
       </c>
       <c r="C20">
-        <v>176.8299817113176</v>
+        <v>175.4331136527134</v>
       </c>
       <c r="D20">
-        <v>213.2419817113176</v>
+        <v>213.9341136527134</v>
       </c>
       <c r="E20">
-        <v>-87.59800000000001</v>
+        <v>-85.509</v>
       </c>
       <c r="F20">
-        <v>37.602</v>
+        <v>39.691</v>
       </c>
       <c r="G20">
         <v>1.19</v>
@@ -2909,28 +2909,28 @@
         <v>23.225</v>
       </c>
       <c r="M20">
-        <v>1.9477836</v>
+        <v>2.0559938</v>
       </c>
       <c r="N20">
-        <v>21.2772164</v>
+        <v>21.1690062</v>
       </c>
       <c r="O20">
-        <v>4.893759771999999</v>
+        <v>4.868871426</v>
       </c>
       <c r="P20">
-        <v>16.383456628</v>
+        <v>16.300134774</v>
       </c>
       <c r="Q20">
-        <v>20.283456628</v>
+        <v>20.200134774</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1178167627145248</v>
+        <v>0.1185309331648753</v>
       </c>
       <c r="T20">
-        <v>1.114076415118563</v>
+        <v>1.125124404852065</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.92380919523093</v>
+        <v>11.29624029021877</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2955,22 +2955,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.103588395863549</v>
+        <v>0.1033875663011876</v>
       </c>
       <c r="C21">
-        <v>175.4331136527134</v>
+        <v>174.0407532107914</v>
       </c>
       <c r="D21">
-        <v>213.9341136527134</v>
+        <v>214.6307532107914</v>
       </c>
       <c r="E21">
-        <v>-85.509</v>
+        <v>-83.42</v>
       </c>
       <c r="F21">
-        <v>39.691</v>
+        <v>41.78</v>
       </c>
       <c r="G21">
         <v>1.19</v>
@@ -2991,28 +2991,28 @@
         <v>23.225</v>
       </c>
       <c r="M21">
-        <v>2.0559938</v>
+        <v>2.164204</v>
       </c>
       <c r="N21">
-        <v>21.1690062</v>
+        <v>21.060796</v>
       </c>
       <c r="O21">
-        <v>4.868871426</v>
+        <v>4.843983079999999</v>
       </c>
       <c r="P21">
-        <v>16.300134774</v>
+        <v>16.21681292</v>
       </c>
       <c r="Q21">
-        <v>20.200134774</v>
+        <v>20.11681291999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1185309331648753</v>
+        <v>0.1192629578764845</v>
       </c>
       <c r="T21">
-        <v>1.125124404852065</v>
+        <v>1.136448594328903</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.29624029021877</v>
+        <v>10.73142827570783</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3037,22 +3037,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1033875663011876</v>
+        <v>0.1031867367388263</v>
       </c>
       <c r="C22">
-        <v>174.0407532107914</v>
+        <v>172.6529445642415</v>
       </c>
       <c r="D22">
-        <v>214.6307532107914</v>
+        <v>215.3319445642415</v>
       </c>
       <c r="E22">
-        <v>-83.42</v>
+        <v>-81.33099999999999</v>
       </c>
       <c r="F22">
-        <v>41.78</v>
+        <v>43.86900000000001</v>
       </c>
       <c r="G22">
         <v>1.19</v>
@@ -3073,28 +3073,28 @@
         <v>23.225</v>
       </c>
       <c r="M22">
-        <v>2.164204</v>
+        <v>2.2724142</v>
       </c>
       <c r="N22">
-        <v>21.060796</v>
+        <v>20.9525858</v>
       </c>
       <c r="O22">
-        <v>4.843983079999999</v>
+        <v>4.819094734</v>
       </c>
       <c r="P22">
-        <v>16.21681292</v>
+        <v>16.133491066</v>
       </c>
       <c r="Q22">
-        <v>20.11681291999999</v>
+        <v>20.033491066</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1192629578764845</v>
+        <v>0.1200135148592738</v>
       </c>
       <c r="T22">
-        <v>1.136448594328903</v>
+        <v>1.148059472146928</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.73142827570783</v>
+        <v>10.22040788162651</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3119,22 +3119,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1031867367388263</v>
+        <v>0.1032738871764649</v>
       </c>
       <c r="C23">
-        <v>172.6529445642415</v>
+        <v>170.2590991061444</v>
       </c>
       <c r="D23">
-        <v>215.3319445642415</v>
+        <v>215.0270991061444</v>
       </c>
       <c r="E23">
-        <v>-81.331</v>
+        <v>-79.242</v>
       </c>
       <c r="F23">
-        <v>43.869</v>
+        <v>45.958</v>
       </c>
       <c r="G23">
         <v>1.19</v>
@@ -3155,45 +3155,45 @@
         <v>23.225</v>
       </c>
       <c r="M23">
-        <v>2.2724142</v>
+        <v>2.458753</v>
       </c>
       <c r="N23">
-        <v>20.9525858</v>
+        <v>20.766247</v>
       </c>
       <c r="O23">
-        <v>4.819094734</v>
+        <v>4.77623681</v>
       </c>
       <c r="P23">
-        <v>16.133491066</v>
+        <v>15.99001019</v>
       </c>
       <c r="Q23">
-        <v>20.033491066</v>
+        <v>19.89001019</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1200135148592738</v>
+        <v>0.1207833168929038</v>
       </c>
       <c r="T23">
-        <v>1.148059472146928</v>
+        <v>1.1599680647808</v>
       </c>
       <c r="U23">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V23">
         <v>0.23</v>
       </c>
       <c r="W23">
-        <v>0.039886</v>
+        <v>0.041195</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>10.22040788162651</v>
+        <v>9.44584510928914</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3201,22 +3201,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1032738871764649</v>
+        <v>0.1030861476141036</v>
       </c>
       <c r="C24">
-        <v>170.2590991061444</v>
+        <v>168.8278738347185</v>
       </c>
       <c r="D24">
-        <v>215.0270991061444</v>
+        <v>215.6848738347185</v>
       </c>
       <c r="E24">
-        <v>-79.242</v>
+        <v>-77.15299999999999</v>
       </c>
       <c r="F24">
-        <v>45.958</v>
+        <v>48.047</v>
       </c>
       <c r="G24">
         <v>1.19</v>
@@ -3237,28 +3237,28 @@
         <v>23.225</v>
       </c>
       <c r="M24">
-        <v>2.458753</v>
+        <v>2.5705145</v>
       </c>
       <c r="N24">
-        <v>20.766247</v>
+        <v>20.6544855</v>
       </c>
       <c r="O24">
-        <v>4.77623681</v>
+        <v>4.750531665</v>
       </c>
       <c r="P24">
-        <v>15.99001019</v>
+        <v>15.903953835</v>
       </c>
       <c r="Q24">
-        <v>19.89001019</v>
+        <v>19.80395383499999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1207833168929038</v>
+        <v>0.1215731137845501</v>
       </c>
       <c r="T24">
-        <v>1.1599680647808</v>
+        <v>1.172185971509058</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.44584510928914</v>
+        <v>9.035156191493957</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3283,22 +3283,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1030861476141036</v>
+        <v>0.1028984080517422</v>
       </c>
       <c r="C25">
-        <v>168.8278738347185</v>
+        <v>167.4006852191419</v>
       </c>
       <c r="D25">
-        <v>215.6848738347185</v>
+        <v>216.3466852191419</v>
       </c>
       <c r="E25">
-        <v>-77.15299999999999</v>
+        <v>-75.06399999999999</v>
       </c>
       <c r="F25">
-        <v>48.047</v>
+        <v>50.136</v>
       </c>
       <c r="G25">
         <v>1.19</v>
@@ -3319,28 +3319,28 @@
         <v>23.225</v>
       </c>
       <c r="M25">
-        <v>2.5705145</v>
+        <v>2.682276</v>
       </c>
       <c r="N25">
-        <v>20.6544855</v>
+        <v>20.542724</v>
       </c>
       <c r="O25">
-        <v>4.750531665</v>
+        <v>4.724826520000001</v>
       </c>
       <c r="P25">
-        <v>15.903953835</v>
+        <v>15.81789748</v>
       </c>
       <c r="Q25">
-        <v>19.80395383499999</v>
+        <v>19.71789748</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1215731137845501</v>
+        <v>0.1223836948049239</v>
       </c>
       <c r="T25">
-        <v>1.172185971509058</v>
+        <v>1.184725402098585</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.035156191493957</v>
+        <v>8.658691350181712</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3365,22 +3365,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1028984080517422</v>
+        <v>0.1027106684893809</v>
       </c>
       <c r="C26">
-        <v>167.4006852191419</v>
+        <v>165.977570532227</v>
       </c>
       <c r="D26">
-        <v>216.3466852191419</v>
+        <v>217.012570532227</v>
       </c>
       <c r="E26">
-        <v>-75.06399999999999</v>
+        <v>-72.97499999999999</v>
       </c>
       <c r="F26">
-        <v>50.136</v>
+        <v>52.225</v>
       </c>
       <c r="G26">
         <v>1.19</v>
@@ -3401,28 +3401,28 @@
         <v>23.225</v>
       </c>
       <c r="M26">
-        <v>2.682276</v>
+        <v>2.7940375</v>
       </c>
       <c r="N26">
-        <v>20.542724</v>
+        <v>20.4309625</v>
       </c>
       <c r="O26">
-        <v>4.724826520000001</v>
+        <v>4.699121375</v>
       </c>
       <c r="P26">
-        <v>15.81789748</v>
+        <v>15.731841125</v>
       </c>
       <c r="Q26">
-        <v>19.71789748</v>
+        <v>19.631841125</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1223836948049239</v>
+        <v>0.1232158913191745</v>
       </c>
       <c r="T26">
-        <v>1.184725402098585</v>
+        <v>1.197599217503834</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.658691350181712</v>
+        <v>8.312343696174443</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3447,22 +3447,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1027106684893809</v>
+        <v>0.1025229289270195</v>
       </c>
       <c r="C27">
-        <v>165.977570532227</v>
+        <v>164.5585675070862</v>
       </c>
       <c r="D27">
-        <v>217.012570532227</v>
+        <v>217.6825675070862</v>
       </c>
       <c r="E27">
-        <v>-72.97499999999999</v>
+        <v>-70.886</v>
       </c>
       <c r="F27">
-        <v>52.225</v>
+        <v>54.314</v>
       </c>
       <c r="G27">
         <v>1.19</v>
@@ -3483,28 +3483,28 @@
         <v>23.225</v>
       </c>
       <c r="M27">
-        <v>2.7940375</v>
+        <v>2.905799</v>
       </c>
       <c r="N27">
-        <v>20.4309625</v>
+        <v>20.319201</v>
       </c>
       <c r="O27">
-        <v>4.699121375</v>
+        <v>4.67341623</v>
       </c>
       <c r="P27">
-        <v>15.731841125</v>
+        <v>15.64578477</v>
       </c>
       <c r="Q27">
-        <v>19.631841125</v>
+        <v>19.54578477</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1232158913191745</v>
+        <v>0.1240705796311075</v>
       </c>
       <c r="T27">
-        <v>1.197599217503834</v>
+        <v>1.210820973865981</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.312343696174443</v>
+        <v>7.992638169398503</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3529,22 +3529,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1025229289270195</v>
+        <v>0.1023351893646581</v>
       </c>
       <c r="C28">
-        <v>164.5585675070862</v>
+        <v>163.1437143442581</v>
       </c>
       <c r="D28">
-        <v>217.6825675070862</v>
+        <v>218.3567143442581</v>
       </c>
       <c r="E28">
-        <v>-70.886</v>
+        <v>-68.797</v>
       </c>
       <c r="F28">
-        <v>54.314</v>
+        <v>56.40300000000001</v>
       </c>
       <c r="G28">
         <v>1.19</v>
@@ -3565,28 +3565,28 @@
         <v>23.225</v>
       </c>
       <c r="M28">
-        <v>2.905799</v>
+        <v>3.0175605</v>
       </c>
       <c r="N28">
-        <v>20.319201</v>
+        <v>20.2074395</v>
       </c>
       <c r="O28">
-        <v>4.67341623</v>
+        <v>4.647711085</v>
       </c>
       <c r="P28">
-        <v>15.64578477</v>
+        <v>15.559728415</v>
       </c>
       <c r="Q28">
-        <v>19.54578477</v>
+        <v>19.459728415</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1240705796311075</v>
+        <v>0.1249486840611755</v>
       </c>
       <c r="T28">
-        <v>1.210820973865981</v>
+        <v>1.224404970128461</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.992638169398503</v>
+        <v>7.696614533494854</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3611,22 +3611,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1023351893646581</v>
+        <v>0.1023199298022968</v>
       </c>
       <c r="C29">
-        <v>163.1437143442581</v>
+        <v>161.1096928601738</v>
       </c>
       <c r="D29">
-        <v>218.3567143442581</v>
+        <v>218.4116928601738</v>
       </c>
       <c r="E29">
-        <v>-68.797</v>
+        <v>-66.708</v>
       </c>
       <c r="F29">
-        <v>56.40300000000001</v>
+        <v>58.492</v>
       </c>
       <c r="G29">
         <v>1.19</v>
@@ -3647,45 +3647,45 @@
         <v>23.225</v>
       </c>
       <c r="M29">
-        <v>3.0175605</v>
+        <v>3.1761156</v>
       </c>
       <c r="N29">
-        <v>20.2074395</v>
+        <v>20.0488844</v>
       </c>
       <c r="O29">
-        <v>4.647711085</v>
+        <v>4.611243412</v>
       </c>
       <c r="P29">
-        <v>15.559728415</v>
+        <v>15.437640988</v>
       </c>
       <c r="Q29">
-        <v>19.459728415</v>
+        <v>19.337640988</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1249486840611755</v>
+        <v>0.1258511802809678</v>
       </c>
       <c r="T29">
-        <v>1.224404970128461</v>
+        <v>1.238366299620455</v>
       </c>
       <c r="U29">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V29">
         <v>0.23</v>
       </c>
       <c r="W29">
-        <v>0.041195</v>
+        <v>0.041811</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y29">
-        <v>7.696614533494854</v>
+        <v>7.312391274423386</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1023199298022968</v>
+        <v>0.1021383502399354</v>
       </c>
       <c r="C30">
-        <v>161.1096928601738</v>
+        <v>159.6770351096668</v>
       </c>
       <c r="D30">
-        <v>218.4116928601738</v>
+        <v>219.0680351096669</v>
       </c>
       <c r="E30">
-        <v>-66.708</v>
+        <v>-64.619</v>
       </c>
       <c r="F30">
-        <v>58.492</v>
+        <v>60.58100000000001</v>
       </c>
       <c r="G30">
         <v>1.19</v>
@@ -3729,28 +3729,28 @@
         <v>23.225</v>
       </c>
       <c r="M30">
-        <v>3.1761156</v>
+        <v>3.289548300000001</v>
       </c>
       <c r="N30">
-        <v>20.0488844</v>
+        <v>19.9354517</v>
       </c>
       <c r="O30">
-        <v>4.611243412</v>
+        <v>4.585153891</v>
       </c>
       <c r="P30">
-        <v>15.437640988</v>
+        <v>15.350297809</v>
       </c>
       <c r="Q30">
-        <v>19.337640988</v>
+        <v>19.250297809</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1258511802809678</v>
+        <v>0.1267790989294866</v>
       </c>
       <c r="T30">
-        <v>1.238366299620455</v>
+        <v>1.252720905999546</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.312391274423386</v>
+        <v>7.060239851167406</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3775,22 +3775,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1021383502399354</v>
+        <v>0.1019567706775741</v>
       </c>
       <c r="C31">
-        <v>159.6770351096669</v>
+        <v>158.2483339567568</v>
       </c>
       <c r="D31">
-        <v>219.0680351096669</v>
+        <v>219.7283339567568</v>
       </c>
       <c r="E31">
-        <v>-64.619</v>
+        <v>-62.53</v>
       </c>
       <c r="F31">
-        <v>60.581</v>
+        <v>62.67</v>
       </c>
       <c r="G31">
         <v>1.19</v>
@@ -3811,28 +3811,28 @@
         <v>23.225</v>
       </c>
       <c r="M31">
-        <v>3.2895483</v>
+        <v>3.402981</v>
       </c>
       <c r="N31">
-        <v>19.9354517</v>
+        <v>19.822019</v>
       </c>
       <c r="O31">
-        <v>4.585153891</v>
+        <v>4.55906437</v>
       </c>
       <c r="P31">
-        <v>15.350297809</v>
+        <v>15.26295463</v>
       </c>
       <c r="Q31">
-        <v>19.250297809</v>
+        <v>19.16295462999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1267790989294866</v>
+        <v>0.1277335295393915</v>
       </c>
       <c r="T31">
-        <v>1.252720905999546</v>
+        <v>1.267485643989469</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.060239851167408</v>
+        <v>6.82489852279516</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3857,22 +3857,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1019567706775741</v>
+        <v>0.1017751911152127</v>
       </c>
       <c r="C32">
-        <v>158.2483339567568</v>
+        <v>156.8236252866674</v>
       </c>
       <c r="D32">
-        <v>219.7283339567568</v>
+        <v>220.3926252866674</v>
       </c>
       <c r="E32">
-        <v>-62.53</v>
+        <v>-60.441</v>
       </c>
       <c r="F32">
-        <v>62.67</v>
+        <v>64.759</v>
       </c>
       <c r="G32">
         <v>1.19</v>
@@ -3893,28 +3893,28 @@
         <v>23.225</v>
       </c>
       <c r="M32">
-        <v>3.402981</v>
+        <v>3.5164137</v>
       </c>
       <c r="N32">
-        <v>19.822019</v>
+        <v>19.7085863</v>
       </c>
       <c r="O32">
-        <v>4.55906437</v>
+        <v>4.532974848999999</v>
       </c>
       <c r="P32">
-        <v>15.26295463</v>
+        <v>15.175611451</v>
       </c>
       <c r="Q32">
-        <v>19.16295462999999</v>
+        <v>19.075611451</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1277335295393915</v>
+        <v>0.1287156248046561</v>
       </c>
       <c r="T32">
-        <v>1.267485643989469</v>
+        <v>1.28267834539939</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.82489852279516</v>
+        <v>6.6047405059308</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3939,22 +3939,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1017751911152127</v>
+        <v>0.1015936115528514</v>
       </c>
       <c r="C33">
-        <v>156.8236252866674</v>
+        <v>155.4029454198969</v>
       </c>
       <c r="D33">
-        <v>220.3926252866674</v>
+        <v>221.0609454198969</v>
       </c>
       <c r="E33">
-        <v>-60.441</v>
+        <v>-58.352</v>
       </c>
       <c r="F33">
-        <v>64.759</v>
+        <v>66.848</v>
       </c>
       <c r="G33">
         <v>1.19</v>
@@ -3975,28 +3975,28 @@
         <v>23.225</v>
       </c>
       <c r="M33">
-        <v>3.5164137</v>
+        <v>3.6298464</v>
       </c>
       <c r="N33">
-        <v>19.7085863</v>
+        <v>19.5951536</v>
       </c>
       <c r="O33">
-        <v>4.532974848999999</v>
+        <v>4.506885327999999</v>
       </c>
       <c r="P33">
-        <v>15.175611451</v>
+        <v>15.088268272</v>
       </c>
       <c r="Q33">
-        <v>19.075611451</v>
+        <v>18.988268272</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1287156248046561</v>
+        <v>0.1297266052247814</v>
       </c>
       <c r="T33">
-        <v>1.28267834539939</v>
+        <v>1.298317890968425</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.6047405059308</v>
+        <v>6.398342365120462</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4021,22 +4021,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1015936115528514</v>
+        <v>0.10141203199049</v>
       </c>
       <c r="C34">
-        <v>155.4029454198969</v>
+        <v>153.9863311188376</v>
       </c>
       <c r="D34">
-        <v>221.0609454198969</v>
+        <v>221.7333311188376</v>
       </c>
       <c r="E34">
-        <v>-58.352</v>
+        <v>-56.26299999999999</v>
       </c>
       <c r="F34">
-        <v>66.848</v>
+        <v>68.93700000000001</v>
       </c>
       <c r="G34">
         <v>1.19</v>
@@ -4057,28 +4057,28 @@
         <v>23.225</v>
       </c>
       <c r="M34">
-        <v>3.6298464</v>
+        <v>3.743279100000001</v>
       </c>
       <c r="N34">
-        <v>19.5951536</v>
+        <v>19.4817209</v>
       </c>
       <c r="O34">
-        <v>4.506885327999999</v>
+        <v>4.480795807</v>
       </c>
       <c r="P34">
-        <v>15.088268272</v>
+        <v>15.000925093</v>
       </c>
       <c r="Q34">
-        <v>18.988268272</v>
+        <v>18.900925093</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1297266052247814</v>
+        <v>0.1307677641649105</v>
       </c>
       <c r="T34">
-        <v>1.298317890968425</v>
+        <v>1.314424288644</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.398342365120462</v>
+        <v>6.204453202541054</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4103,22 +4103,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.10141203199049</v>
+        <v>0.1014922524281287</v>
       </c>
       <c r="C35">
-        <v>153.9863311188376</v>
+        <v>151.599772668297</v>
       </c>
       <c r="D35">
-        <v>221.7333311188376</v>
+        <v>221.435772668297</v>
       </c>
       <c r="E35">
-        <v>-56.26299999999999</v>
+        <v>-54.17399999999999</v>
       </c>
       <c r="F35">
-        <v>68.93700000000001</v>
+        <v>71.02600000000001</v>
       </c>
       <c r="G35">
         <v>1.19</v>
@@ -4139,45 +4139,45 @@
         <v>23.225</v>
       </c>
       <c r="M35">
-        <v>3.743279100000001</v>
+        <v>3.927737800000001</v>
       </c>
       <c r="N35">
-        <v>19.4817209</v>
+        <v>19.2972622</v>
       </c>
       <c r="O35">
-        <v>4.480795807</v>
+        <v>4.438370305999999</v>
       </c>
       <c r="P35">
-        <v>15.000925093</v>
+        <v>14.858891894</v>
       </c>
       <c r="Q35">
-        <v>18.900925093</v>
+        <v>18.758891894</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1307677641649105</v>
+        <v>0.1318404733759525</v>
       </c>
       <c r="T35">
-        <v>1.314424288644</v>
+        <v>1.33101875897641</v>
       </c>
       <c r="U35">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V35">
         <v>0.23</v>
       </c>
       <c r="W35">
-        <v>0.041811</v>
+        <v>0.042581</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>6.204453202541054</v>
+        <v>5.913072914388531</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4185,22 +4185,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1014922524281287</v>
+        <v>0.1013183728657673</v>
       </c>
       <c r="C36">
-        <v>151.599772668297</v>
+        <v>150.1567506136847</v>
       </c>
       <c r="D36">
-        <v>221.435772668297</v>
+        <v>222.0817506136847</v>
       </c>
       <c r="E36">
-        <v>-54.17399999999999</v>
+        <v>-52.08499999999999</v>
       </c>
       <c r="F36">
-        <v>71.02600000000001</v>
+        <v>73.11500000000001</v>
       </c>
       <c r="G36">
         <v>1.19</v>
@@ -4221,28 +4221,28 @@
         <v>23.225</v>
       </c>
       <c r="M36">
-        <v>3.927737800000001</v>
+        <v>4.0432595</v>
       </c>
       <c r="N36">
-        <v>19.2972622</v>
+        <v>19.1817405</v>
       </c>
       <c r="O36">
-        <v>4.438370305999999</v>
+        <v>4.411800315</v>
       </c>
       <c r="P36">
-        <v>14.858891894</v>
+        <v>14.769940185</v>
       </c>
       <c r="Q36">
-        <v>18.758891894</v>
+        <v>18.66994018499999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1318404733759525</v>
+        <v>0.1329461890242574</v>
       </c>
       <c r="T36">
-        <v>1.33101875897641</v>
+        <v>1.348123828395971</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.913072914388531</v>
+        <v>5.744127973977429</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4267,22 +4267,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1013183728657673</v>
+        <v>0.101144493303406</v>
       </c>
       <c r="C37">
-        <v>150.1567506136847</v>
+        <v>148.7175085119134</v>
       </c>
       <c r="D37">
-        <v>222.0817506136847</v>
+        <v>222.7315085119134</v>
       </c>
       <c r="E37">
-        <v>-52.08499999999999</v>
+        <v>-49.996</v>
       </c>
       <c r="F37">
-        <v>73.11500000000001</v>
+        <v>75.20400000000001</v>
       </c>
       <c r="G37">
         <v>1.19</v>
@@ -4303,28 +4303,28 @@
         <v>23.225</v>
       </c>
       <c r="M37">
-        <v>4.0432595</v>
+        <v>4.158781200000001</v>
       </c>
       <c r="N37">
-        <v>19.1817405</v>
+        <v>19.0662188</v>
       </c>
       <c r="O37">
-        <v>4.411800315</v>
+        <v>4.385230324</v>
       </c>
       <c r="P37">
-        <v>14.769940185</v>
+        <v>14.680988476</v>
       </c>
       <c r="Q37">
-        <v>18.66994018499999</v>
+        <v>18.58098847599999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1329461890242574</v>
+        <v>0.1340864582865718</v>
       </c>
       <c r="T37">
-        <v>1.348123828395971</v>
+        <v>1.365763431234893</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.744127973977429</v>
+        <v>5.584568863589167</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4349,22 +4349,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.101144493303406</v>
+        <v>0.1009706137410446</v>
       </c>
       <c r="C38">
-        <v>148.7175085119134</v>
+        <v>147.2820796380423</v>
       </c>
       <c r="D38">
-        <v>222.7315085119134</v>
+        <v>223.3850796380423</v>
       </c>
       <c r="E38">
-        <v>-49.99600000000001</v>
+        <v>-47.907</v>
       </c>
       <c r="F38">
-        <v>75.20399999999999</v>
+        <v>77.29300000000001</v>
       </c>
       <c r="G38">
         <v>1.19</v>
@@ -4385,28 +4385,28 @@
         <v>23.225</v>
       </c>
       <c r="M38">
-        <v>4.1587812</v>
+        <v>4.2743029</v>
       </c>
       <c r="N38">
-        <v>19.0662188</v>
+        <v>18.9506971</v>
       </c>
       <c r="O38">
-        <v>4.385230324</v>
+        <v>4.358660333</v>
       </c>
       <c r="P38">
-        <v>14.680988476</v>
+        <v>14.592036767</v>
       </c>
       <c r="Q38">
-        <v>18.58098847599999</v>
+        <v>18.492036767</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1340864582865718</v>
+        <v>0.1352629265730867</v>
       </c>
       <c r="T38">
-        <v>1.365763431234893</v>
+        <v>1.383963021465527</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.584568863589168</v>
+        <v>5.433634569978651</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4431,22 +4431,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1009706137410446</v>
+        <v>0.1007967341786833</v>
       </c>
       <c r="C39">
-        <v>147.2820796380423</v>
+        <v>145.8504976588421</v>
       </c>
       <c r="D39">
-        <v>223.3850796380423</v>
+        <v>224.0424976588421</v>
       </c>
       <c r="E39">
-        <v>-47.907</v>
+        <v>-45.818</v>
       </c>
       <c r="F39">
-        <v>77.29300000000001</v>
+        <v>79.38200000000001</v>
       </c>
       <c r="G39">
         <v>1.19</v>
@@ -4467,28 +4467,28 @@
         <v>23.225</v>
       </c>
       <c r="M39">
-        <v>4.2743029</v>
+        <v>4.389824600000001</v>
       </c>
       <c r="N39">
-        <v>18.9506971</v>
+        <v>18.8351754</v>
       </c>
       <c r="O39">
-        <v>4.358660333</v>
+        <v>4.332090342</v>
       </c>
       <c r="P39">
-        <v>14.592036767</v>
+        <v>14.503085058</v>
       </c>
       <c r="Q39">
-        <v>18.492036767</v>
+        <v>18.40308505799999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1352629265730867</v>
+        <v>0.1364773454494891</v>
       </c>
       <c r="T39">
-        <v>1.383963021465527</v>
+        <v>1.402749695251988</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.433634569978651</v>
+        <v>5.290644186558159</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4513,22 +4513,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1007967341786833</v>
+        <v>0.1006228546163219</v>
       </c>
       <c r="C40">
-        <v>145.8504976588421</v>
+        <v>144.4227966385756</v>
       </c>
       <c r="D40">
-        <v>224.0424976588421</v>
+        <v>224.7037966385756</v>
       </c>
       <c r="E40">
-        <v>-45.818</v>
+        <v>-43.729</v>
       </c>
       <c r="F40">
-        <v>79.38200000000001</v>
+        <v>81.471</v>
       </c>
       <c r="G40">
         <v>1.19</v>
@@ -4549,28 +4549,28 @@
         <v>23.225</v>
       </c>
       <c r="M40">
-        <v>4.389824600000001</v>
+        <v>4.5053463</v>
       </c>
       <c r="N40">
-        <v>18.8351754</v>
+        <v>18.7196537</v>
       </c>
       <c r="O40">
-        <v>4.332090342</v>
+        <v>4.305520351</v>
       </c>
       <c r="P40">
-        <v>14.503085058</v>
+        <v>14.414133349</v>
       </c>
       <c r="Q40">
-        <v>18.40308505799999</v>
+        <v>18.314133349</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1364773454494891</v>
+        <v>0.1377315813382326</v>
       </c>
       <c r="T40">
-        <v>1.402749695251988</v>
+        <v>1.422152325556038</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.290644186558159</v>
+        <v>5.154986643313078</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4595,22 +4595,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1006228546163219</v>
+        <v>0.1004489750539605</v>
       </c>
       <c r="C41">
-        <v>144.4227966385756</v>
+        <v>142.9990110448819</v>
       </c>
       <c r="D41">
-        <v>224.7037966385756</v>
+        <v>225.3690110448819</v>
       </c>
       <c r="E41">
-        <v>-43.729</v>
+        <v>-41.64</v>
       </c>
       <c r="F41">
-        <v>81.471</v>
+        <v>83.56</v>
       </c>
       <c r="G41">
         <v>1.19</v>
@@ -4631,28 +4631,28 @@
         <v>23.225</v>
       </c>
       <c r="M41">
-        <v>4.5053463</v>
+        <v>4.620868000000001</v>
       </c>
       <c r="N41">
-        <v>18.7196537</v>
+        <v>18.604132</v>
       </c>
       <c r="O41">
-        <v>4.305520351</v>
+        <v>4.27895036</v>
       </c>
       <c r="P41">
-        <v>14.414133349</v>
+        <v>14.32518164</v>
       </c>
       <c r="Q41">
-        <v>18.314133349</v>
+        <v>18.22518164</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1377315813382326</v>
+        <v>0.1390276250899342</v>
       </c>
       <c r="T41">
-        <v>1.422152325556038</v>
+        <v>1.442201710203556</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4669,7 +4669,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.154986643313078</v>
+        <v>5.026111977230251</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4677,22 +4677,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1004489750539605</v>
+        <v>0.1002750954915992</v>
       </c>
       <c r="C42">
-        <v>142.9990110448819</v>
+        <v>141.5791757547649</v>
       </c>
       <c r="D42">
-        <v>225.3690110448819</v>
+        <v>226.038175754765</v>
       </c>
       <c r="E42">
-        <v>-41.64</v>
+        <v>-39.55099999999999</v>
       </c>
       <c r="F42">
-        <v>83.56</v>
+        <v>85.64900000000002</v>
       </c>
       <c r="G42">
         <v>1.19</v>
@@ -4713,28 +4713,28 @@
         <v>23.225</v>
       </c>
       <c r="M42">
-        <v>4.620868000000001</v>
+        <v>4.736389700000001</v>
       </c>
       <c r="N42">
-        <v>18.604132</v>
+        <v>18.4886103</v>
       </c>
       <c r="O42">
-        <v>4.27895036</v>
+        <v>4.252380369</v>
       </c>
       <c r="P42">
-        <v>14.32518164</v>
+        <v>14.236229931</v>
       </c>
       <c r="Q42">
-        <v>18.22518164</v>
+        <v>18.136229931</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1390276250899342</v>
+        <v>0.1403676025281342</v>
       </c>
       <c r="T42">
-        <v>1.442201710203556</v>
+        <v>1.462930735008617</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.026111977230251</v>
+        <v>4.903523880224634</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1002750954915992</v>
+        <v>0.1001012159292378</v>
       </c>
       <c r="C43">
-        <v>141.5791757547649</v>
+        <v>140.1633260606889</v>
       </c>
       <c r="D43">
-        <v>226.038175754765</v>
+        <v>226.7113260606889</v>
       </c>
       <c r="E43">
-        <v>-39.55099999999999</v>
+        <v>-37.46199999999999</v>
       </c>
       <c r="F43">
-        <v>85.64900000000002</v>
+        <v>87.73800000000001</v>
       </c>
       <c r="G43">
         <v>1.19</v>
@@ -4795,28 +4795,28 @@
         <v>23.225</v>
       </c>
       <c r="M43">
-        <v>4.736389700000001</v>
+        <v>4.851911400000001</v>
       </c>
       <c r="N43">
-        <v>18.4886103</v>
+        <v>18.3730886</v>
       </c>
       <c r="O43">
-        <v>4.252380369</v>
+        <v>4.225810377999999</v>
       </c>
       <c r="P43">
-        <v>14.236229931</v>
+        <v>14.147278222</v>
       </c>
       <c r="Q43">
-        <v>18.136229931</v>
+        <v>18.047278222</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1403676025281342</v>
+        <v>0.1417537860848928</v>
       </c>
       <c r="T43">
-        <v>1.462930735008617</v>
+        <v>1.484374553772474</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.903523880224634</v>
+        <v>4.786773311647858</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4841,22 +4841,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1001012159292379</v>
+        <v>0.09992733636687649</v>
       </c>
       <c r="C44">
-        <v>140.1633260606887</v>
+        <v>138.7514976767823</v>
       </c>
       <c r="D44">
-        <v>226.7113260606887</v>
+        <v>227.3884976767823</v>
       </c>
       <c r="E44">
-        <v>-37.462</v>
+        <v>-35.373</v>
       </c>
       <c r="F44">
-        <v>87.738</v>
+        <v>89.827</v>
       </c>
       <c r="G44">
         <v>1.19</v>
@@ -4877,28 +4877,28 @@
         <v>23.225</v>
       </c>
       <c r="M44">
-        <v>4.851911400000001</v>
+        <v>4.9674331</v>
       </c>
       <c r="N44">
-        <v>18.3730886</v>
+        <v>18.2575669</v>
       </c>
       <c r="O44">
-        <v>4.225810377999999</v>
+        <v>4.199240387</v>
       </c>
       <c r="P44">
-        <v>14.147278222</v>
+        <v>14.058326513</v>
       </c>
       <c r="Q44">
-        <v>18.047278222</v>
+        <v>17.958326513</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1417537860848928</v>
+        <v>0.1431886076611868</v>
       </c>
       <c r="T44">
-        <v>1.484374553772474</v>
+        <v>1.506570787229799</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.786773311647858</v>
+        <v>4.675453002074653</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4923,22 +4923,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09992733636687649</v>
+        <v>0.09975345680451514</v>
       </c>
       <c r="C45">
-        <v>138.7514976767823</v>
+        <v>137.3437267451557</v>
       </c>
       <c r="D45">
-        <v>227.3884976767823</v>
+        <v>228.0697267451557</v>
       </c>
       <c r="E45">
-        <v>-35.373</v>
+        <v>-33.28400000000001</v>
       </c>
       <c r="F45">
-        <v>89.827</v>
+        <v>91.916</v>
       </c>
       <c r="G45">
         <v>1.19</v>
@@ -4959,28 +4959,28 @@
         <v>23.225</v>
       </c>
       <c r="M45">
-        <v>4.9674331</v>
+        <v>5.0829548</v>
       </c>
       <c r="N45">
-        <v>18.2575669</v>
+        <v>18.1420452</v>
       </c>
       <c r="O45">
-        <v>4.199240387</v>
+        <v>4.172670396</v>
       </c>
       <c r="P45">
-        <v>14.058326513</v>
+        <v>13.969374804</v>
       </c>
       <c r="Q45">
-        <v>17.958326513</v>
+        <v>17.869374804</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1431886076611868</v>
+        <v>0.1446746728652056</v>
       </c>
       <c r="T45">
-        <v>1.506570787229799</v>
+        <v>1.5295597433106</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.675453002074653</v>
+        <v>4.569192706572956</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5005,22 +5005,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09975345680451514</v>
+        <v>0.1004458272421538</v>
       </c>
       <c r="C46">
-        <v>137.3437267451557</v>
+        <v>132.5660899878872</v>
       </c>
       <c r="D46">
-        <v>228.0697267451557</v>
+        <v>225.3810899878872</v>
       </c>
       <c r="E46">
-        <v>-33.28400000000001</v>
+        <v>-31.19499999999999</v>
       </c>
       <c r="F46">
-        <v>91.916</v>
+        <v>94.00500000000001</v>
       </c>
       <c r="G46">
         <v>1.19</v>
@@ -5041,45 +5041,45 @@
         <v>23.225</v>
       </c>
       <c r="M46">
-        <v>5.0829548</v>
+        <v>5.433489000000001</v>
       </c>
       <c r="N46">
-        <v>18.1420452</v>
+        <v>17.791511</v>
       </c>
       <c r="O46">
-        <v>4.172670396</v>
+        <v>4.092047529999999</v>
       </c>
       <c r="P46">
-        <v>13.969374804</v>
+        <v>13.69946347</v>
       </c>
       <c r="Q46">
-        <v>17.869374804</v>
+        <v>17.59946347</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1446746728652056</v>
+        <v>0.146214776803916</v>
       </c>
       <c r="T46">
-        <v>1.5295597433106</v>
+        <v>1.553384661430702</v>
       </c>
       <c r="U46">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V46">
         <v>0.23</v>
       </c>
       <c r="W46">
-        <v>0.042581</v>
+        <v>0.044506</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.569192706572956</v>
+        <v>4.274417413930532</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5087,22 +5087,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1004458272421538</v>
+        <v>0.1002911976797924</v>
       </c>
       <c r="C47">
-        <v>132.5660899878872</v>
+        <v>131.0720405713147</v>
       </c>
       <c r="D47">
-        <v>225.3810899878872</v>
+        <v>225.9760405713147</v>
       </c>
       <c r="E47">
-        <v>-31.19499999999999</v>
+        <v>-29.10599999999999</v>
       </c>
       <c r="F47">
-        <v>94.00500000000001</v>
+        <v>96.09400000000001</v>
       </c>
       <c r="G47">
         <v>1.19</v>
@@ -5123,28 +5123,28 @@
         <v>23.225</v>
       </c>
       <c r="M47">
-        <v>5.433489000000001</v>
+        <v>5.554233200000001</v>
       </c>
       <c r="N47">
-        <v>17.791511</v>
+        <v>17.6707668</v>
       </c>
       <c r="O47">
-        <v>4.092047529999999</v>
+        <v>4.064276363999999</v>
       </c>
       <c r="P47">
-        <v>13.69946347</v>
+        <v>13.606490436</v>
       </c>
       <c r="Q47">
-        <v>17.59946347</v>
+        <v>17.50649043599999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.146214776803916</v>
+        <v>0.1478119216292453</v>
       </c>
       <c r="T47">
-        <v>1.553384661430702</v>
+        <v>1.578091983925624</v>
       </c>
       <c r="U47">
         <v>0.0578</v>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.274417413930532</v>
+        <v>4.18149529623639</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5169,22 +5169,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1002911976797924</v>
+        <v>0.1001365681174311</v>
       </c>
       <c r="C48">
-        <v>131.0720405713147</v>
+        <v>129.5811405143751</v>
       </c>
       <c r="D48">
-        <v>225.9760405713147</v>
+        <v>226.5741405143751</v>
       </c>
       <c r="E48">
-        <v>-29.10599999999999</v>
+        <v>-27.017</v>
       </c>
       <c r="F48">
-        <v>96.09400000000001</v>
+        <v>98.18300000000001</v>
       </c>
       <c r="G48">
         <v>1.19</v>
@@ -5205,28 +5205,28 @@
         <v>23.225</v>
       </c>
       <c r="M48">
-        <v>5.554233200000001</v>
+        <v>5.6749774</v>
       </c>
       <c r="N48">
-        <v>17.6707668</v>
+        <v>17.5500226</v>
       </c>
       <c r="O48">
-        <v>4.064276363999999</v>
+        <v>4.036505198</v>
       </c>
       <c r="P48">
-        <v>13.606490436</v>
+        <v>13.513517402</v>
       </c>
       <c r="Q48">
-        <v>17.50649043599999</v>
+        <v>17.413517402</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1478119216292453</v>
+        <v>0.1494693360706247</v>
       </c>
       <c r="T48">
-        <v>1.578091983925624</v>
+        <v>1.603731658212806</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.18149529623639</v>
+        <v>4.092527311210085</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5251,22 +5251,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1001365681174311</v>
+        <v>0.09998193855506973</v>
       </c>
       <c r="C49">
-        <v>129.5811405143751</v>
+        <v>128.093414890043</v>
       </c>
       <c r="D49">
-        <v>226.5741405143751</v>
+        <v>227.175414890043</v>
       </c>
       <c r="E49">
-        <v>-27.017</v>
+        <v>-24.928</v>
       </c>
       <c r="F49">
-        <v>98.18300000000001</v>
+        <v>100.272</v>
       </c>
       <c r="G49">
         <v>1.19</v>
@@ -5287,28 +5287,28 @@
         <v>23.225</v>
       </c>
       <c r="M49">
-        <v>5.6749774</v>
+        <v>5.795721600000001</v>
       </c>
       <c r="N49">
-        <v>17.5500226</v>
+        <v>17.4292784</v>
       </c>
       <c r="O49">
-        <v>4.036505198</v>
+        <v>4.008734032</v>
       </c>
       <c r="P49">
-        <v>13.513517402</v>
+        <v>13.420544368</v>
       </c>
       <c r="Q49">
-        <v>17.413517402</v>
+        <v>17.320544368</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1494693360706247</v>
+        <v>0.1511904972212879</v>
       </c>
       <c r="T49">
-        <v>1.603731658212806</v>
+        <v>1.630357473818727</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.092527311210085</v>
+        <v>4.007266325559874</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5333,22 +5333,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09998193855506973</v>
+        <v>0.1011478589927084</v>
       </c>
       <c r="C50">
-        <v>128.093414890043</v>
+        <v>121.5478954292183</v>
       </c>
       <c r="D50">
-        <v>227.175414890043</v>
+        <v>222.7188954292183</v>
       </c>
       <c r="E50">
-        <v>-24.928</v>
+        <v>-22.839</v>
       </c>
       <c r="F50">
-        <v>100.272</v>
+        <v>102.361</v>
       </c>
       <c r="G50">
         <v>1.19</v>
@@ -5369,45 +5369,45 @@
         <v>23.225</v>
       </c>
       <c r="M50">
-        <v>5.795721600000001</v>
+        <v>6.274729300000001</v>
       </c>
       <c r="N50">
-        <v>17.4292784</v>
+        <v>16.9502707</v>
       </c>
       <c r="O50">
-        <v>4.008734032</v>
+        <v>3.898562260999999</v>
       </c>
       <c r="P50">
-        <v>13.420544368</v>
+        <v>13.051708439</v>
       </c>
       <c r="Q50">
-        <v>17.320544368</v>
+        <v>16.951708439</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1511904972212879</v>
+        <v>0.1529791548876635</v>
       </c>
       <c r="T50">
-        <v>1.630357473818727</v>
+        <v>1.658027439056252</v>
       </c>
       <c r="U50">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V50">
         <v>0.23</v>
       </c>
       <c r="W50">
-        <v>0.044506</v>
+        <v>0.047201</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>4.007266325559874</v>
+        <v>3.701354893509111</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5415,22 +5415,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1011478589927084</v>
+        <v>0.101020179430347</v>
       </c>
       <c r="C51">
-        <v>121.5478954292183</v>
+        <v>119.938383705591</v>
       </c>
       <c r="D51">
-        <v>222.7188954292183</v>
+        <v>223.198383705591</v>
       </c>
       <c r="E51">
-        <v>-22.839</v>
+        <v>-20.75</v>
       </c>
       <c r="F51">
-        <v>102.361</v>
+        <v>104.45</v>
       </c>
       <c r="G51">
         <v>1.19</v>
@@ -5451,28 +5451,28 @@
         <v>23.225</v>
       </c>
       <c r="M51">
-        <v>6.274729300000001</v>
+        <v>6.402785000000001</v>
       </c>
       <c r="N51">
-        <v>16.9502707</v>
+        <v>16.822215</v>
       </c>
       <c r="O51">
-        <v>3.898562260999999</v>
+        <v>3.869109449999999</v>
       </c>
       <c r="P51">
-        <v>13.051708439</v>
+        <v>12.95310555</v>
       </c>
       <c r="Q51">
-        <v>16.951708439</v>
+        <v>16.85310555</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1529791548876635</v>
+        <v>0.154839358860694</v>
       </c>
       <c r="T51">
-        <v>1.658027439056252</v>
+        <v>1.686804202903278</v>
       </c>
       <c r="U51">
         <v>0.0613</v>
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.701354893509111</v>
+        <v>3.627327795638928</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5497,22 +5497,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.101020179430347</v>
+        <v>0.1008924998679857</v>
       </c>
       <c r="C52">
-        <v>119.938383705591</v>
+        <v>118.3309410030264</v>
       </c>
       <c r="D52">
-        <v>223.198383705591</v>
+        <v>223.6799410030264</v>
       </c>
       <c r="E52">
-        <v>-20.75</v>
+        <v>-18.661</v>
       </c>
       <c r="F52">
-        <v>104.45</v>
+        <v>106.539</v>
       </c>
       <c r="G52">
         <v>1.19</v>
@@ -5533,28 +5533,28 @@
         <v>23.225</v>
       </c>
       <c r="M52">
-        <v>6.402785000000001</v>
+        <v>6.5308407</v>
       </c>
       <c r="N52">
-        <v>16.822215</v>
+        <v>16.6941593</v>
       </c>
       <c r="O52">
-        <v>3.869109449999999</v>
+        <v>3.839656639</v>
       </c>
       <c r="P52">
-        <v>12.95310555</v>
+        <v>12.854502661</v>
       </c>
       <c r="Q52">
-        <v>16.85310555</v>
+        <v>16.754502661</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.154839358860694</v>
+        <v>0.1567754895265014</v>
       </c>
       <c r="T52">
-        <v>1.686804202903278</v>
+        <v>1.716755528539979</v>
       </c>
       <c r="U52">
         <v>0.0613</v>
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.627327795638928</v>
+        <v>3.556203721214636</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5579,22 +5579,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1008924998679857</v>
+        <v>0.1018859403056243</v>
       </c>
       <c r="C53">
-        <v>118.3309410030264</v>
+        <v>112.5489831137553</v>
       </c>
       <c r="D53">
-        <v>223.6799410030264</v>
+        <v>219.9869831137553</v>
       </c>
       <c r="E53">
-        <v>-18.661</v>
+        <v>-16.572</v>
       </c>
       <c r="F53">
-        <v>106.539</v>
+        <v>108.628</v>
       </c>
       <c r="G53">
         <v>1.19</v>
@@ -5615,45 +5615,45 @@
         <v>23.225</v>
       </c>
       <c r="M53">
-        <v>6.5308407</v>
+        <v>6.9630548</v>
       </c>
       <c r="N53">
-        <v>16.6941593</v>
+        <v>16.2619452</v>
       </c>
       <c r="O53">
-        <v>3.839656639</v>
+        <v>3.740247396</v>
       </c>
       <c r="P53">
-        <v>12.854502661</v>
+        <v>12.521697804</v>
       </c>
       <c r="Q53">
-        <v>16.754502661</v>
+        <v>16.421697804</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1567754895265014</v>
+        <v>0.158792292303384</v>
       </c>
       <c r="T53">
-        <v>1.716755528539979</v>
+        <v>1.747954826078209</v>
       </c>
       <c r="U53">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V53">
         <v>0.23</v>
       </c>
       <c r="W53">
-        <v>0.047201</v>
+        <v>0.04935700000000001</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y53">
-        <v>3.556203721214636</v>
+        <v>3.335461326543057</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5661,22 +5661,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1018859403056243</v>
+        <v>0.101779820743263</v>
       </c>
       <c r="C54">
-        <v>112.5489831137553</v>
+        <v>110.8486383432417</v>
       </c>
       <c r="D54">
-        <v>219.9869831137553</v>
+        <v>220.3756383432417</v>
       </c>
       <c r="E54">
-        <v>-16.572</v>
+        <v>-14.48299999999999</v>
       </c>
       <c r="F54">
-        <v>108.628</v>
+        <v>110.717</v>
       </c>
       <c r="G54">
         <v>1.19</v>
@@ -5697,28 +5697,28 @@
         <v>23.225</v>
       </c>
       <c r="M54">
-        <v>6.9630548</v>
+        <v>7.096959700000001</v>
       </c>
       <c r="N54">
-        <v>16.2619452</v>
+        <v>16.12804029999999</v>
       </c>
       <c r="O54">
-        <v>3.740247396</v>
+        <v>3.709449268999999</v>
       </c>
       <c r="P54">
-        <v>12.521697804</v>
+        <v>12.418591031</v>
       </c>
       <c r="Q54">
-        <v>16.421697804</v>
+        <v>16.318591031</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.158792292303384</v>
+        <v>0.1608949164750276</v>
       </c>
       <c r="T54">
-        <v>1.747954826078209</v>
+        <v>1.780481753298917</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.335461326543057</v>
+        <v>3.272528093966772</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5743,22 +5743,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.101779820743263</v>
+        <v>0.1016737011809016</v>
       </c>
       <c r="C55">
-        <v>110.8486383432417</v>
+        <v>109.1496692925606</v>
       </c>
       <c r="D55">
-        <v>220.3756383432417</v>
+        <v>220.7656692925606</v>
       </c>
       <c r="E55">
-        <v>-14.48299999999999</v>
+        <v>-12.39399999999999</v>
       </c>
       <c r="F55">
-        <v>110.717</v>
+        <v>112.806</v>
       </c>
       <c r="G55">
         <v>1.19</v>
@@ -5779,28 +5779,28 @@
         <v>23.225</v>
       </c>
       <c r="M55">
-        <v>7.096959700000001</v>
+        <v>7.230864600000001</v>
       </c>
       <c r="N55">
-        <v>16.12804029999999</v>
+        <v>15.9941354</v>
       </c>
       <c r="O55">
-        <v>3.709449268999999</v>
+        <v>3.678651142</v>
       </c>
       <c r="P55">
-        <v>12.418591031</v>
+        <v>12.315484258</v>
       </c>
       <c r="Q55">
-        <v>16.318591031</v>
+        <v>16.215484258</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1608949164750276</v>
+        <v>0.1630889590889165</v>
       </c>
       <c r="T55">
-        <v>1.780481753298917</v>
+        <v>1.814422894746611</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.272528093966772</v>
+        <v>3.211925721856276</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1016737011809016</v>
+        <v>0.1015675816185402</v>
       </c>
       <c r="C56">
-        <v>109.1496692925606</v>
+        <v>107.4520832790992</v>
       </c>
       <c r="D56">
-        <v>220.7656692925606</v>
+        <v>221.1570832790992</v>
       </c>
       <c r="E56">
-        <v>-12.39399999999999</v>
+        <v>-10.30499999999999</v>
       </c>
       <c r="F56">
-        <v>112.806</v>
+        <v>114.895</v>
       </c>
       <c r="G56">
         <v>1.19</v>
@@ -5861,28 +5861,28 @@
         <v>23.225</v>
       </c>
       <c r="M56">
-        <v>7.230864600000001</v>
+        <v>7.364769500000001</v>
       </c>
       <c r="N56">
-        <v>15.9941354</v>
+        <v>15.8602305</v>
       </c>
       <c r="O56">
-        <v>3.678651142</v>
+        <v>3.647853014999999</v>
       </c>
       <c r="P56">
-        <v>12.315484258</v>
+        <v>12.212377485</v>
       </c>
       <c r="Q56">
-        <v>16.215484258</v>
+        <v>16.112377485</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1630889590889165</v>
+        <v>0.1653805147078672</v>
       </c>
       <c r="T56">
-        <v>1.814422894746611</v>
+        <v>1.849872531369759</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.211925721856276</v>
+        <v>3.15352707236798</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5907,22 +5907,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1015675816185402</v>
+        <v>0.1014614620561789</v>
       </c>
       <c r="C57">
-        <v>107.4520832790992</v>
+        <v>105.7558876722316</v>
       </c>
       <c r="D57">
-        <v>221.1570832790992</v>
+        <v>221.5498876722316</v>
       </c>
       <c r="E57">
-        <v>-10.30499999999999</v>
+        <v>-8.215999999999994</v>
       </c>
       <c r="F57">
-        <v>114.895</v>
+        <v>116.984</v>
       </c>
       <c r="G57">
         <v>1.19</v>
@@ -5943,28 +5943,28 @@
         <v>23.225</v>
       </c>
       <c r="M57">
-        <v>7.364769500000001</v>
+        <v>7.498674400000001</v>
       </c>
       <c r="N57">
-        <v>15.8602305</v>
+        <v>15.7263256</v>
       </c>
       <c r="O57">
-        <v>3.647853014999999</v>
+        <v>3.617054887999999</v>
       </c>
       <c r="P57">
-        <v>12.212377485</v>
+        <v>12.109270712</v>
       </c>
       <c r="Q57">
-        <v>16.112377485</v>
+        <v>16.009270712</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1653805147078672</v>
+        <v>0.1677762319458611</v>
       </c>
       <c r="T57">
-        <v>1.849872531369759</v>
+        <v>1.886933515112142</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.15352707236798</v>
+        <v>3.097214088932838</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5989,22 +5989,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1014614620561789</v>
+        <v>0.1013553424938175</v>
       </c>
       <c r="C58">
-        <v>105.7558876722316</v>
+        <v>104.0610898937814</v>
       </c>
       <c r="D58">
-        <v>221.5498876722316</v>
+        <v>221.9440898937814</v>
       </c>
       <c r="E58">
-        <v>-8.215999999999994</v>
+        <v>-6.126999999999981</v>
       </c>
       <c r="F58">
-        <v>116.984</v>
+        <v>119.073</v>
       </c>
       <c r="G58">
         <v>1.19</v>
@@ -6025,28 +6025,28 @@
         <v>23.225</v>
       </c>
       <c r="M58">
-        <v>7.498674400000001</v>
+        <v>7.632579300000002</v>
       </c>
       <c r="N58">
-        <v>15.7263256</v>
+        <v>15.5924207</v>
       </c>
       <c r="O58">
-        <v>3.617054887999999</v>
+        <v>3.586256760999999</v>
       </c>
       <c r="P58">
-        <v>12.109270712</v>
+        <v>12.006163939</v>
       </c>
       <c r="Q58">
-        <v>16.009270712</v>
+        <v>15.906163939</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1677762319458611</v>
+        <v>0.1702833778925989</v>
       </c>
       <c r="T58">
-        <v>1.886933515112142</v>
+        <v>1.925718265540216</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.097214088932838</v>
+        <v>3.042876999653314</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6071,22 +6071,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1013553424938175</v>
+        <v>0.1047327029314562</v>
       </c>
       <c r="C59">
-        <v>104.0610898937814</v>
+        <v>90.07745660990328</v>
       </c>
       <c r="D59">
-        <v>221.9440898937814</v>
+        <v>210.0494566099033</v>
       </c>
       <c r="E59">
-        <v>-6.126999999999981</v>
+        <v>-4.037999999999982</v>
       </c>
       <c r="F59">
-        <v>119.073</v>
+        <v>121.162</v>
       </c>
       <c r="G59">
         <v>1.19</v>
@@ -6107,45 +6107,45 @@
         <v>23.225</v>
       </c>
       <c r="M59">
-        <v>7.632579300000002</v>
+        <v>8.711547800000002</v>
       </c>
       <c r="N59">
-        <v>15.5924207</v>
+        <v>14.5134522</v>
       </c>
       <c r="O59">
-        <v>3.586256760999999</v>
+        <v>3.338094005999999</v>
       </c>
       <c r="P59">
-        <v>12.006163939</v>
+        <v>11.175358194</v>
       </c>
       <c r="Q59">
-        <v>15.906163939</v>
+        <v>15.075358194</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1702833778925989</v>
+        <v>0.1729099117415623</v>
       </c>
       <c r="T59">
-        <v>1.925718265540216</v>
+        <v>1.966349908845818</v>
       </c>
       <c r="U59">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V59">
         <v>0.23</v>
       </c>
       <c r="W59">
-        <v>0.04935700000000001</v>
+        <v>0.055363</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>3.042876999653314</v>
+        <v>2.666001557151531</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6153,22 +6153,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1047327029314562</v>
+        <v>0.1046866433690948</v>
       </c>
       <c r="C60">
-        <v>90.07745660990322</v>
+        <v>88.14209118587131</v>
       </c>
       <c r="D60">
-        <v>210.0494566099032</v>
+        <v>210.2030911858713</v>
       </c>
       <c r="E60">
-        <v>-4.038000000000011</v>
+        <v>-1.949000000000012</v>
       </c>
       <c r="F60">
-        <v>121.162</v>
+        <v>123.251</v>
       </c>
       <c r="G60">
         <v>1.19</v>
@@ -6189,28 +6189,28 @@
         <v>23.225</v>
       </c>
       <c r="M60">
-        <v>8.7115478</v>
+        <v>8.8617469</v>
       </c>
       <c r="N60">
-        <v>14.5134522</v>
+        <v>14.3632531</v>
       </c>
       <c r="O60">
-        <v>3.338094006</v>
+        <v>3.303548213</v>
       </c>
       <c r="P60">
-        <v>11.175358194</v>
+        <v>11.059704887</v>
       </c>
       <c r="Q60">
-        <v>15.075358194</v>
+        <v>14.959704887</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1729099117415623</v>
+        <v>0.1756645691929142</v>
       </c>
       <c r="T60">
-        <v>1.966349908845818</v>
+        <v>2.00896358353218</v>
       </c>
       <c r="U60">
         <v>0.07190000000000001</v>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.666001557151532</v>
+        <v>2.620815090081166</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6235,22 +6235,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1046866433690948</v>
+        <v>0.1046405838067335</v>
       </c>
       <c r="C61">
-        <v>88.14209118587131</v>
+        <v>86.20695066944072</v>
       </c>
       <c r="D61">
-        <v>210.2030911858713</v>
+        <v>210.3569506694407</v>
       </c>
       <c r="E61">
-        <v>-1.949000000000012</v>
+        <v>0.1400000000000006</v>
       </c>
       <c r="F61">
-        <v>123.251</v>
+        <v>125.34</v>
       </c>
       <c r="G61">
         <v>1.19</v>
@@ -6271,28 +6271,28 @@
         <v>23.225</v>
       </c>
       <c r="M61">
-        <v>8.8617469</v>
+        <v>9.011946000000002</v>
       </c>
       <c r="N61">
-        <v>14.3632531</v>
+        <v>14.213054</v>
       </c>
       <c r="O61">
-        <v>3.303548213</v>
+        <v>3.269002419999999</v>
       </c>
       <c r="P61">
-        <v>11.059704887</v>
+        <v>10.94405158</v>
       </c>
       <c r="Q61">
-        <v>14.959704887</v>
+        <v>14.84405158</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1756645691929142</v>
+        <v>0.1785569595168337</v>
       </c>
       <c r="T61">
-        <v>2.00896358353218</v>
+        <v>2.053707941952861</v>
       </c>
       <c r="U61">
         <v>0.07190000000000001</v>
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.620815090081166</v>
+        <v>2.577134838579813</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6317,22 +6317,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1046405838067335</v>
+        <v>0.1045945242443721</v>
       </c>
       <c r="C62">
-        <v>86.20695066944072</v>
+        <v>84.27203555484076</v>
       </c>
       <c r="D62">
-        <v>210.3569506694407</v>
+        <v>210.5110355548408</v>
       </c>
       <c r="E62">
-        <v>0.1400000000000006</v>
+        <v>2.228999999999999</v>
       </c>
       <c r="F62">
-        <v>125.34</v>
+        <v>127.429</v>
       </c>
       <c r="G62">
         <v>1.19</v>
@@ -6353,28 +6353,28 @@
         <v>23.225</v>
       </c>
       <c r="M62">
-        <v>9.011946000000002</v>
+        <v>9.1621451</v>
       </c>
       <c r="N62">
-        <v>14.213054</v>
+        <v>14.0628549</v>
       </c>
       <c r="O62">
-        <v>3.269002419999999</v>
+        <v>3.234456627</v>
       </c>
       <c r="P62">
-        <v>10.94405158</v>
+        <v>10.828398273</v>
       </c>
       <c r="Q62">
-        <v>14.84405158</v>
+        <v>14.728398273</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1785569595168337</v>
+        <v>0.1815976775496721</v>
       </c>
       <c r="T62">
-        <v>2.053707941952861</v>
+        <v>2.100746882856654</v>
       </c>
       <c r="U62">
         <v>0.07190000000000001</v>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.577134838579813</v>
+        <v>2.534886726471948</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6399,22 +6399,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1045945242443721</v>
+        <v>0.1064103246820108</v>
       </c>
       <c r="C63">
-        <v>84.27203555484076</v>
+        <v>76.27473053921338</v>
       </c>
       <c r="D63">
-        <v>210.5110355548408</v>
+        <v>204.6027305392134</v>
       </c>
       <c r="E63">
-        <v>2.228999999999999</v>
+        <v>4.317999999999998</v>
       </c>
       <c r="F63">
-        <v>127.429</v>
+        <v>129.518</v>
       </c>
       <c r="G63">
         <v>1.19</v>
@@ -6435,45 +6435,45 @@
         <v>23.225</v>
       </c>
       <c r="M63">
-        <v>9.1621451</v>
+        <v>9.8174644</v>
       </c>
       <c r="N63">
-        <v>14.0628549</v>
+        <v>13.4075356</v>
       </c>
       <c r="O63">
-        <v>3.234456627</v>
+        <v>3.083733188</v>
       </c>
       <c r="P63">
-        <v>10.828398273</v>
+        <v>10.323802412</v>
       </c>
       <c r="Q63">
-        <v>14.728398273</v>
+        <v>14.223802412</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1815976775496721</v>
+        <v>0.1847984333737126</v>
       </c>
       <c r="T63">
-        <v>2.100746882856654</v>
+        <v>2.150261557492225</v>
       </c>
       <c r="U63">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V63">
         <v>0.23</v>
       </c>
       <c r="W63">
-        <v>0.055363</v>
+        <v>0.05836600000000001</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y63">
-        <v>2.534886726471948</v>
+        <v>2.365682120527985</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6481,22 +6481,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1064103246820108</v>
+        <v>0.1063942951196494</v>
       </c>
       <c r="C64">
-        <v>76.27473053921338</v>
+        <v>74.23643668853126</v>
       </c>
       <c r="D64">
-        <v>204.6027305392134</v>
+        <v>204.6534366885313</v>
       </c>
       <c r="E64">
-        <v>4.317999999999998</v>
+        <v>6.406999999999996</v>
       </c>
       <c r="F64">
-        <v>129.518</v>
+        <v>131.607</v>
       </c>
       <c r="G64">
         <v>1.19</v>
@@ -6517,28 +6517,28 @@
         <v>23.225</v>
       </c>
       <c r="M64">
-        <v>9.8174644</v>
+        <v>9.975810600000001</v>
       </c>
       <c r="N64">
-        <v>13.4075356</v>
+        <v>13.2491894</v>
       </c>
       <c r="O64">
-        <v>3.083733188</v>
+        <v>3.047313561999999</v>
       </c>
       <c r="P64">
-        <v>10.323802412</v>
+        <v>10.201875838</v>
       </c>
       <c r="Q64">
-        <v>14.223802412</v>
+        <v>14.101875838</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1847984333737126</v>
+        <v>0.1881722030260795</v>
       </c>
       <c r="T64">
-        <v>2.150261557492225</v>
+        <v>2.202452701027017</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.365682120527985</v>
+        <v>2.328131610678334</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6563,22 +6563,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1063942951196494</v>
+        <v>0.106378265557288</v>
       </c>
       <c r="C65">
-        <v>74.23643668853126</v>
+        <v>72.19816797681898</v>
       </c>
       <c r="D65">
-        <v>204.6534366885313</v>
+        <v>204.704167976819</v>
       </c>
       <c r="E65">
-        <v>6.406999999999996</v>
+        <v>8.495999999999995</v>
       </c>
       <c r="F65">
-        <v>131.607</v>
+        <v>133.696</v>
       </c>
       <c r="G65">
         <v>1.19</v>
@@ -6599,28 +6599,28 @@
         <v>23.225</v>
       </c>
       <c r="M65">
-        <v>9.975810600000001</v>
+        <v>10.1341568</v>
       </c>
       <c r="N65">
-        <v>13.2491894</v>
+        <v>13.0908432</v>
       </c>
       <c r="O65">
-        <v>3.047313561999999</v>
+        <v>3.010893936</v>
       </c>
       <c r="P65">
-        <v>10.201875838</v>
+        <v>10.079949264</v>
       </c>
       <c r="Q65">
-        <v>14.101875838</v>
+        <v>13.97994926399999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1881722030260795</v>
+        <v>0.1917334043258002</v>
       </c>
       <c r="T65">
-        <v>2.202452701027017</v>
+        <v>2.257543352535963</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.328131610678334</v>
+        <v>2.291754554261485</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6645,22 +6645,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.106378265557288</v>
+        <v>0.1063622359949267</v>
       </c>
       <c r="C66">
-        <v>72.19816797681898</v>
+        <v>70.15992442277596</v>
       </c>
       <c r="D66">
-        <v>204.704167976819</v>
+        <v>204.754924422776</v>
       </c>
       <c r="E66">
-        <v>8.495999999999995</v>
+        <v>10.58499999999999</v>
       </c>
       <c r="F66">
-        <v>133.696</v>
+        <v>135.785</v>
       </c>
       <c r="G66">
         <v>1.19</v>
@@ -6681,28 +6681,28 @@
         <v>23.225</v>
       </c>
       <c r="M66">
-        <v>10.1341568</v>
+        <v>10.292503</v>
       </c>
       <c r="N66">
-        <v>13.0908432</v>
+        <v>12.932497</v>
       </c>
       <c r="O66">
-        <v>3.010893936</v>
+        <v>2.97447431</v>
       </c>
       <c r="P66">
-        <v>10.079949264</v>
+        <v>9.958022689999998</v>
       </c>
       <c r="Q66">
-        <v>13.97994926399999</v>
+        <v>13.85802269</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1917334043258002</v>
+        <v>0.1954981028426478</v>
       </c>
       <c r="T66">
-        <v>2.257543352535963</v>
+        <v>2.315782041273992</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.291754554261485</v>
+        <v>2.256496791888232</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6727,22 +6727,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1063622359949267</v>
+        <v>0.1063462064325654</v>
       </c>
       <c r="C67">
-        <v>70.15992442277596</v>
+        <v>68.12170604512065</v>
       </c>
       <c r="D67">
-        <v>204.754924422776</v>
+        <v>204.8057060451207</v>
       </c>
       <c r="E67">
-        <v>10.58499999999999</v>
+        <v>12.67400000000002</v>
       </c>
       <c r="F67">
-        <v>135.785</v>
+        <v>137.874</v>
       </c>
       <c r="G67">
         <v>1.19</v>
@@ -6763,28 +6763,28 @@
         <v>23.225</v>
       </c>
       <c r="M67">
-        <v>10.292503</v>
+        <v>10.4508492</v>
       </c>
       <c r="N67">
-        <v>12.932497</v>
+        <v>12.7741508</v>
       </c>
       <c r="O67">
-        <v>2.97447431</v>
+        <v>2.938054683999999</v>
       </c>
       <c r="P67">
-        <v>9.958022689999998</v>
+        <v>9.836096115999997</v>
       </c>
       <c r="Q67">
-        <v>13.85802269</v>
+        <v>13.736096116</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1954981028426478</v>
+        <v>0.1994842542134275</v>
       </c>
       <c r="T67">
-        <v>2.315782041273992</v>
+        <v>2.377446535231905</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.256496791888232</v>
+        <v>2.222307446556591</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6809,22 +6809,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1063462064325654</v>
+        <v>0.106330176870204</v>
       </c>
       <c r="C68">
-        <v>68.12170604512065</v>
+        <v>66.08351286258966</v>
       </c>
       <c r="D68">
-        <v>204.8057060451207</v>
+        <v>204.8565128625897</v>
       </c>
       <c r="E68">
-        <v>12.67400000000002</v>
+        <v>14.76300000000002</v>
       </c>
       <c r="F68">
-        <v>137.874</v>
+        <v>139.963</v>
       </c>
       <c r="G68">
         <v>1.19</v>
@@ -6845,28 +6845,28 @@
         <v>23.225</v>
       </c>
       <c r="M68">
-        <v>10.4508492</v>
+        <v>10.6091954</v>
       </c>
       <c r="N68">
-        <v>12.7741508</v>
+        <v>12.6158046</v>
       </c>
       <c r="O68">
-        <v>2.938054683999999</v>
+        <v>2.901635057999999</v>
       </c>
       <c r="P68">
-        <v>9.836096115999997</v>
+        <v>9.714169541999997</v>
       </c>
       <c r="Q68">
-        <v>13.736096116</v>
+        <v>13.614169542</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1994842542134275</v>
+        <v>0.2037119905157697</v>
       </c>
       <c r="T68">
-        <v>2.377446535231905</v>
+        <v>2.442848271247874</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.222307446556591</v>
+        <v>2.189138678697538</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.106330176870204</v>
+        <v>0.1063141473078427</v>
       </c>
       <c r="C69">
-        <v>66.08351286258966</v>
+        <v>64.04534489393839</v>
       </c>
       <c r="D69">
-        <v>204.8565128625897</v>
+        <v>204.9073448939384</v>
       </c>
       <c r="E69">
-        <v>14.76300000000002</v>
+        <v>16.85200000000002</v>
       </c>
       <c r="F69">
-        <v>139.963</v>
+        <v>142.052</v>
       </c>
       <c r="G69">
         <v>1.19</v>
@@ -6927,28 +6927,28 @@
         <v>23.225</v>
       </c>
       <c r="M69">
-        <v>10.6091954</v>
+        <v>10.7675416</v>
       </c>
       <c r="N69">
-        <v>12.6158046</v>
+        <v>12.45745839999999</v>
       </c>
       <c r="O69">
-        <v>2.901635057999999</v>
+        <v>2.865215431999999</v>
       </c>
       <c r="P69">
-        <v>9.714169541999997</v>
+        <v>9.592242967999995</v>
       </c>
       <c r="Q69">
-        <v>13.614169542</v>
+        <v>13.49224296799999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2037119905157697</v>
+        <v>0.2082039603370083</v>
       </c>
       <c r="T69">
-        <v>2.442848271247874</v>
+        <v>2.51233761576484</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.189138678697538</v>
+        <v>2.156945462834338</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6973,22 +6973,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1063141473078427</v>
+        <v>0.1062981177454813</v>
       </c>
       <c r="C70">
-        <v>64.04534489393839</v>
+        <v>62.00720215794087</v>
       </c>
       <c r="D70">
-        <v>204.9073448939384</v>
+        <v>204.9582021579409</v>
       </c>
       <c r="E70">
-        <v>16.85200000000002</v>
+        <v>18.94100000000002</v>
       </c>
       <c r="F70">
-        <v>142.052</v>
+        <v>144.141</v>
       </c>
       <c r="G70">
         <v>1.19</v>
@@ -7009,28 +7009,28 @@
         <v>23.225</v>
       </c>
       <c r="M70">
-        <v>10.7675416</v>
+        <v>10.9258878</v>
       </c>
       <c r="N70">
-        <v>12.45745839999999</v>
+        <v>12.2991122</v>
       </c>
       <c r="O70">
-        <v>2.865215431999999</v>
+        <v>2.828795805999999</v>
       </c>
       <c r="P70">
-        <v>9.592242967999995</v>
+        <v>9.470316393999997</v>
       </c>
       <c r="Q70">
-        <v>13.49224296799999</v>
+        <v>13.370316394</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2082039603370083</v>
+        <v>0.2129857346628429</v>
       </c>
       <c r="T70">
-        <v>2.51233761576484</v>
+        <v>2.586310143799031</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.156945462834338</v>
+        <v>2.125685383662827</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7055,22 +7055,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1062981177454813</v>
+        <v>0.1062820881831199</v>
       </c>
       <c r="C71">
-        <v>62.00720215794087</v>
+        <v>59.96908467338966</v>
       </c>
       <c r="D71">
-        <v>204.9582021579409</v>
+        <v>205.0090846733897</v>
       </c>
       <c r="E71">
-        <v>18.94100000000002</v>
+        <v>21.03000000000002</v>
       </c>
       <c r="F71">
-        <v>144.141</v>
+        <v>146.23</v>
       </c>
       <c r="G71">
         <v>1.19</v>
@@ -7091,28 +7091,28 @@
         <v>23.225</v>
       </c>
       <c r="M71">
-        <v>10.9258878</v>
+        <v>11.084234</v>
       </c>
       <c r="N71">
-        <v>12.2991122</v>
+        <v>12.140766</v>
       </c>
       <c r="O71">
-        <v>2.828795805999999</v>
+        <v>2.792376179999999</v>
       </c>
       <c r="P71">
-        <v>9.470316393999997</v>
+        <v>9.348389819999996</v>
       </c>
       <c r="Q71">
-        <v>13.370316394</v>
+        <v>13.24838981999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2129857346628429</v>
+        <v>0.2180862939437332</v>
       </c>
       <c r="T71">
-        <v>2.586310143799031</v>
+        <v>2.665214173702167</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.125685383662827</v>
+        <v>2.0953184496105</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7137,22 +7137,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1062820881831199</v>
+        <v>0.1062660586207586</v>
       </c>
       <c r="C72">
-        <v>59.96908467338966</v>
+        <v>57.93099245909607</v>
       </c>
       <c r="D72">
-        <v>205.0090846733897</v>
+        <v>205.0599924590961</v>
       </c>
       <c r="E72">
-        <v>21.03000000000002</v>
+        <v>23.11900000000001</v>
       </c>
       <c r="F72">
-        <v>146.23</v>
+        <v>148.319</v>
       </c>
       <c r="G72">
         <v>1.19</v>
@@ -7173,28 +7173,28 @@
         <v>23.225</v>
       </c>
       <c r="M72">
-        <v>11.084234</v>
+        <v>11.2425802</v>
       </c>
       <c r="N72">
-        <v>12.140766</v>
+        <v>11.9824198</v>
       </c>
       <c r="O72">
-        <v>2.792376179999999</v>
+        <v>2.755956553999999</v>
       </c>
       <c r="P72">
-        <v>9.348389819999996</v>
+        <v>9.226463245999996</v>
       </c>
       <c r="Q72">
-        <v>13.24838981999999</v>
+        <v>13.12646324599999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2180862939437332</v>
+        <v>0.2235386159336503</v>
       </c>
       <c r="T72">
-        <v>2.665214173702167</v>
+        <v>2.749559860840002</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.0953184496105</v>
+        <v>2.065806922151197</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7219,22 +7219,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1062660586207586</v>
+        <v>0.1062500290583972</v>
       </c>
       <c r="C73">
-        <v>57.93099245909605</v>
+        <v>55.89292553389018</v>
       </c>
       <c r="D73">
-        <v>205.059992459096</v>
+        <v>205.1109255338902</v>
       </c>
       <c r="E73">
-        <v>23.11899999999999</v>
+        <v>25.20799999999998</v>
       </c>
       <c r="F73">
-        <v>148.319</v>
+        <v>150.408</v>
       </c>
       <c r="G73">
         <v>1.19</v>
@@ -7255,28 +7255,28 @@
         <v>23.225</v>
       </c>
       <c r="M73">
-        <v>11.2425802</v>
+        <v>11.4009264</v>
       </c>
       <c r="N73">
-        <v>11.9824198</v>
+        <v>11.8240736</v>
       </c>
       <c r="O73">
-        <v>2.755956554</v>
+        <v>2.719536928</v>
       </c>
       <c r="P73">
-        <v>9.226463245999998</v>
+        <v>9.104536671999998</v>
       </c>
       <c r="Q73">
-        <v>13.126463246</v>
+        <v>13.004536672</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2235386159336503</v>
+        <v>0.2293803894942758</v>
       </c>
       <c r="T73">
-        <v>2.749559860840002</v>
+        <v>2.839930239916253</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.065806922151197</v>
+        <v>2.037115159343542</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7301,22 +7301,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1062500290583972</v>
+        <v>0.1062339994960359</v>
       </c>
       <c r="C74">
-        <v>55.89292553389018</v>
+        <v>53.85488391662042</v>
       </c>
       <c r="D74">
-        <v>205.1109255338902</v>
+        <v>205.1618839166204</v>
       </c>
       <c r="E74">
-        <v>25.20799999999998</v>
+        <v>27.29700000000001</v>
       </c>
       <c r="F74">
-        <v>150.408</v>
+        <v>152.497</v>
       </c>
       <c r="G74">
         <v>1.19</v>
@@ -7337,28 +7337,28 @@
         <v>23.225</v>
       </c>
       <c r="M74">
-        <v>11.4009264</v>
+        <v>11.5592726</v>
       </c>
       <c r="N74">
-        <v>11.8240736</v>
+        <v>11.6657274</v>
       </c>
       <c r="O74">
-        <v>2.719536928</v>
+        <v>2.683117301999999</v>
       </c>
       <c r="P74">
-        <v>9.104536671999998</v>
+        <v>8.982610097999997</v>
       </c>
       <c r="Q74">
-        <v>13.004536672</v>
+        <v>12.882610098</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2293803894942758</v>
+        <v>0.2356548870223551</v>
       </c>
       <c r="T74">
-        <v>2.839930239916253</v>
+        <v>2.936994721146302</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.037115159343542</v>
+        <v>2.009209472229247</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7383,22 +7383,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1062339994960359</v>
+        <v>0.1143091299336745</v>
       </c>
       <c r="C75">
-        <v>53.85488391662042</v>
+        <v>28.94469208274913</v>
       </c>
       <c r="D75">
-        <v>205.1618839166204</v>
+        <v>182.3406920827491</v>
       </c>
       <c r="E75">
-        <v>27.29700000000001</v>
+        <v>29.38600000000001</v>
       </c>
       <c r="F75">
-        <v>152.497</v>
+        <v>154.586</v>
       </c>
       <c r="G75">
         <v>1.19</v>
@@ -7419,45 +7419,45 @@
         <v>23.225</v>
       </c>
       <c r="M75">
-        <v>11.5592726</v>
+        <v>13.91274</v>
       </c>
       <c r="N75">
-        <v>11.6657274</v>
+        <v>9.312259999999997</v>
       </c>
       <c r="O75">
-        <v>2.683117301999999</v>
+        <v>2.141819799999999</v>
       </c>
       <c r="P75">
-        <v>8.982610097999997</v>
+        <v>7.170440199999997</v>
       </c>
       <c r="Q75">
-        <v>12.882610098</v>
+        <v>11.0704402</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2356548870223551</v>
+        <v>0.2424120382064404</v>
       </c>
       <c r="T75">
-        <v>2.936994721146302</v>
+        <v>3.041525700932508</v>
       </c>
       <c r="U75">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V75">
         <v>0.23</v>
       </c>
       <c r="W75">
-        <v>0.05836600000000001</v>
+        <v>0.0693</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y75">
-        <v>2.009209472229247</v>
+        <v>1.66933328733233</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7465,22 +7465,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1143091299336745</v>
+        <v>0.1144024403713132</v>
       </c>
       <c r="C76">
-        <v>28.94469208274913</v>
+        <v>26.6216208409833</v>
       </c>
       <c r="D76">
-        <v>182.3406920827491</v>
+        <v>182.1066208409833</v>
       </c>
       <c r="E76">
-        <v>29.38600000000001</v>
+        <v>31.47500000000001</v>
       </c>
       <c r="F76">
-        <v>154.586</v>
+        <v>156.675</v>
       </c>
       <c r="G76">
         <v>1.19</v>
@@ -7501,28 +7501,28 @@
         <v>23.225</v>
       </c>
       <c r="M76">
-        <v>13.91274</v>
+        <v>14.10075</v>
       </c>
       <c r="N76">
-        <v>9.312259999999997</v>
+        <v>9.124249999999998</v>
       </c>
       <c r="O76">
-        <v>2.141819799999999</v>
+        <v>2.0985775</v>
       </c>
       <c r="P76">
-        <v>7.170440199999997</v>
+        <v>7.025672499999999</v>
       </c>
       <c r="Q76">
-        <v>11.0704402</v>
+        <v>10.9256725</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2424120382064404</v>
+        <v>0.2497097614852527</v>
       </c>
       <c r="T76">
-        <v>3.041525700932508</v>
+        <v>3.15441915910161</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.66933328733233</v>
+        <v>1.647075510167899</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7547,22 +7547,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1144024403713132</v>
+        <v>0.1144957508089518</v>
       </c>
       <c r="C77">
-        <v>26.6216208409833</v>
+        <v>24.29914978453579</v>
       </c>
       <c r="D77">
-        <v>182.1066208409833</v>
+        <v>181.8731497845358</v>
       </c>
       <c r="E77">
-        <v>31.47500000000001</v>
+        <v>33.56400000000001</v>
       </c>
       <c r="F77">
-        <v>156.675</v>
+        <v>158.764</v>
       </c>
       <c r="G77">
         <v>1.19</v>
@@ -7583,28 +7583,28 @@
         <v>23.225</v>
       </c>
       <c r="M77">
-        <v>14.10075</v>
+        <v>14.28876</v>
       </c>
       <c r="N77">
-        <v>9.124249999999998</v>
+        <v>8.936239999999998</v>
       </c>
       <c r="O77">
-        <v>2.0985775</v>
+        <v>2.0553352</v>
       </c>
       <c r="P77">
-        <v>7.025672499999999</v>
+        <v>6.880904799999998</v>
       </c>
       <c r="Q77">
-        <v>10.9256725</v>
+        <v>10.7809048</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2497097614852527</v>
+        <v>0.2576156283706326</v>
       </c>
       <c r="T77">
-        <v>3.15441915910161</v>
+        <v>3.276720405451472</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.647075510167899</v>
+        <v>1.625403463981479</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7629,22 +7629,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1144957508089518</v>
+        <v>0.1145890612465904</v>
       </c>
       <c r="C78">
-        <v>24.29914978453579</v>
+        <v>21.97727660794718</v>
       </c>
       <c r="D78">
-        <v>181.8731497845358</v>
+        <v>181.6402766079472</v>
       </c>
       <c r="E78">
-        <v>33.56400000000001</v>
+        <v>35.65300000000001</v>
       </c>
       <c r="F78">
-        <v>158.764</v>
+        <v>160.853</v>
       </c>
       <c r="G78">
         <v>1.19</v>
@@ -7665,28 +7665,28 @@
         <v>23.225</v>
       </c>
       <c r="M78">
-        <v>14.28876</v>
+        <v>14.47677</v>
       </c>
       <c r="N78">
-        <v>8.936239999999998</v>
+        <v>8.748229999999998</v>
       </c>
       <c r="O78">
-        <v>2.0553352</v>
+        <v>2.012092899999999</v>
       </c>
       <c r="P78">
-        <v>6.880904799999998</v>
+        <v>6.736137099999999</v>
       </c>
       <c r="Q78">
-        <v>10.7809048</v>
+        <v>10.6361371</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2576156283706326</v>
+        <v>0.2662089619416976</v>
       </c>
       <c r="T78">
-        <v>3.276720405451472</v>
+        <v>3.409656542788277</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.625403463981479</v>
+        <v>1.604294328085616</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7711,22 +7711,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1145890612465904</v>
+        <v>0.1146823716842291</v>
       </c>
       <c r="C79">
-        <v>21.97727660794718</v>
+        <v>19.65599901755041</v>
       </c>
       <c r="D79">
-        <v>181.6402766079472</v>
+        <v>181.4079990175504</v>
       </c>
       <c r="E79">
-        <v>35.65300000000001</v>
+        <v>37.742</v>
       </c>
       <c r="F79">
-        <v>160.853</v>
+        <v>162.942</v>
       </c>
       <c r="G79">
         <v>1.19</v>
@@ -7747,28 +7747,28 @@
         <v>23.225</v>
       </c>
       <c r="M79">
-        <v>14.47677</v>
+        <v>14.66478</v>
       </c>
       <c r="N79">
-        <v>8.748229999999998</v>
+        <v>8.560219999999997</v>
       </c>
       <c r="O79">
-        <v>2.012092899999999</v>
+        <v>1.968850599999999</v>
       </c>
       <c r="P79">
-        <v>6.736137099999999</v>
+        <v>6.591369399999998</v>
       </c>
       <c r="Q79">
-        <v>10.6361371</v>
+        <v>10.4913694</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2662089619416976</v>
+        <v>0.2755835076555869</v>
       </c>
       <c r="T79">
-        <v>3.409656542788277</v>
+        <v>3.554677783519338</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.604294328085616</v>
+        <v>1.583726452084518</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7793,22 +7793,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1146823716842291</v>
+        <v>0.1147756821218678</v>
       </c>
       <c r="C80">
-        <v>19.65599901755041</v>
+        <v>17.33531473139621</v>
       </c>
       <c r="D80">
-        <v>181.4079990175504</v>
+        <v>181.1763147313962</v>
       </c>
       <c r="E80">
-        <v>37.742</v>
+        <v>39.831</v>
       </c>
       <c r="F80">
-        <v>162.942</v>
+        <v>165.031</v>
       </c>
       <c r="G80">
         <v>1.19</v>
@@ -7829,28 +7829,28 @@
         <v>23.225</v>
       </c>
       <c r="M80">
-        <v>14.66478</v>
+        <v>14.85279</v>
       </c>
       <c r="N80">
-        <v>8.560219999999997</v>
+        <v>8.372209999999997</v>
       </c>
       <c r="O80">
-        <v>1.968850599999999</v>
+        <v>1.925608299999999</v>
       </c>
       <c r="P80">
-        <v>6.591369399999998</v>
+        <v>6.446601699999998</v>
       </c>
       <c r="Q80">
-        <v>10.4913694</v>
+        <v>10.3466017</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2755835076555869</v>
+        <v>0.2858508672469893</v>
       </c>
       <c r="T80">
-        <v>3.554677783519338</v>
+        <v>3.71351057098669</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7867,7 +7867,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.583726452084518</v>
+        <v>1.563679281804967</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7875,22 +7875,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1147756821218678</v>
+        <v>0.1148689925595064</v>
       </c>
       <c r="C81">
-        <v>17.33531473139621</v>
+        <v>15.01522147917771</v>
       </c>
       <c r="D81">
-        <v>181.1763147313962</v>
+        <v>180.9452214791777</v>
       </c>
       <c r="E81">
-        <v>39.831</v>
+        <v>41.92</v>
       </c>
       <c r="F81">
-        <v>165.031</v>
+        <v>167.12</v>
       </c>
       <c r="G81">
         <v>1.19</v>
@@ -7911,28 +7911,28 @@
         <v>23.225</v>
       </c>
       <c r="M81">
-        <v>14.85279</v>
+        <v>15.0408</v>
       </c>
       <c r="N81">
-        <v>8.372209999999997</v>
+        <v>8.184199999999999</v>
       </c>
       <c r="O81">
-        <v>1.925608299999999</v>
+        <v>1.882366</v>
       </c>
       <c r="P81">
-        <v>6.446601699999998</v>
+        <v>6.301833999999999</v>
       </c>
       <c r="Q81">
-        <v>10.3466017</v>
+        <v>10.201834</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2858508672469893</v>
+        <v>0.2971449627975321</v>
       </c>
       <c r="T81">
-        <v>3.71351057098669</v>
+        <v>3.888226637200777</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.563679281804967</v>
+        <v>1.544133290782405</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7957,22 +7957,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1148689925595064</v>
+        <v>0.114962302997145</v>
       </c>
       <c r="C82">
-        <v>15.01522147917771</v>
+        <v>12.69571700215658</v>
       </c>
       <c r="D82">
-        <v>180.9452214791777</v>
+        <v>180.7147170021566</v>
       </c>
       <c r="E82">
-        <v>41.92</v>
+        <v>44.009</v>
       </c>
       <c r="F82">
-        <v>167.12</v>
+        <v>169.209</v>
       </c>
       <c r="G82">
         <v>1.19</v>
@@ -7993,28 +7993,28 @@
         <v>23.225</v>
       </c>
       <c r="M82">
-        <v>15.0408</v>
+        <v>15.22881</v>
       </c>
       <c r="N82">
-        <v>8.184199999999999</v>
+        <v>7.996189999999999</v>
       </c>
       <c r="O82">
-        <v>1.882366</v>
+        <v>1.8391237</v>
       </c>
       <c r="P82">
-        <v>6.301833999999999</v>
+        <v>6.157066299999999</v>
       </c>
       <c r="Q82">
-        <v>10.201834</v>
+        <v>10.0570663</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2971449627975321</v>
+        <v>0.3096279105112897</v>
       </c>
       <c r="T82">
-        <v>3.888226637200777</v>
+        <v>4.081333868279505</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8031,7 +8031,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.544133290782405</v>
+        <v>1.525069916822129</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8039,22 +8039,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.114962302997145</v>
+        <v>0.1150556134347837</v>
       </c>
       <c r="C83">
-        <v>12.69571700215658</v>
+        <v>10.3767990530894</v>
       </c>
       <c r="D83">
-        <v>180.7147170021566</v>
+        <v>180.4847990530894</v>
       </c>
       <c r="E83">
-        <v>44.009</v>
+        <v>46.09800000000003</v>
       </c>
       <c r="F83">
-        <v>169.209</v>
+        <v>171.298</v>
       </c>
       <c r="G83">
         <v>1.19</v>
@@ -8075,28 +8075,28 @@
         <v>23.225</v>
       </c>
       <c r="M83">
-        <v>15.22881</v>
+        <v>15.41682</v>
       </c>
       <c r="N83">
-        <v>7.996189999999999</v>
+        <v>7.808179999999997</v>
       </c>
       <c r="O83">
-        <v>1.8391237</v>
+        <v>1.795881399999999</v>
       </c>
       <c r="P83">
-        <v>6.157066299999999</v>
+        <v>6.012298599999998</v>
       </c>
       <c r="Q83">
-        <v>10.0570663</v>
+        <v>9.912298599999996</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3096279105112897</v>
+        <v>0.323497852415465</v>
       </c>
       <c r="T83">
-        <v>4.081333868279505</v>
+        <v>4.295897458366981</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.525069916822129</v>
+        <v>1.506471503202346</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8121,22 +8121,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1150556134347837</v>
+        <v>0.1549325847392324</v>
       </c>
       <c r="C84">
-        <v>10.3767990530894</v>
+        <v>-55.2811172037253</v>
       </c>
       <c r="D84">
-        <v>180.4847990530894</v>
+        <v>116.9158827962747</v>
       </c>
       <c r="E84">
-        <v>46.09800000000003</v>
+        <v>48.18700000000003</v>
       </c>
       <c r="F84">
-        <v>171.298</v>
+        <v>173.387</v>
       </c>
       <c r="G84">
         <v>1.19</v>
@@ -8157,45 +8157,45 @@
         <v>23.225</v>
       </c>
       <c r="M84">
-        <v>15.41682</v>
+        <v>25.45321160000001</v>
       </c>
       <c r="N84">
-        <v>7.808179999999997</v>
+        <v>-2.228211600000009</v>
       </c>
       <c r="O84">
-        <v>1.795881399999999</v>
+        <v>-0.512488668000002</v>
       </c>
       <c r="P84">
-        <v>6.012298599999998</v>
+        <v>-1.715722932000007</v>
       </c>
       <c r="Q84">
-        <v>9.912298599999996</v>
+        <v>2.184277067999992</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.323497852415465</v>
+        <v>0.3450554825564064</v>
       </c>
       <c r="T84">
-        <v>4.295897458366981</v>
+        <v>4.629387140499388</v>
       </c>
       <c r="U84">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.23</v>
+        <v>0.2098654615357065</v>
       </c>
       <c r="W84">
-        <v>0.0693</v>
+        <v>0.1159917502465583</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y84">
-        <v>1.506471503202346</v>
+        <v>0.9124585284161152</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8203,22 +8203,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1549325847392324</v>
+        <v>0.1559425847392325</v>
       </c>
       <c r="C85">
-        <v>-55.2811172037253</v>
+        <v>-58.40387744862191</v>
       </c>
       <c r="D85">
-        <v>116.9158827962747</v>
+        <v>115.8821225513781</v>
       </c>
       <c r="E85">
-        <v>48.18700000000003</v>
+        <v>50.27600000000002</v>
       </c>
       <c r="F85">
-        <v>173.387</v>
+        <v>175.476</v>
       </c>
       <c r="G85">
         <v>1.19</v>
@@ -8239,37 +8239,37 @@
         <v>23.225</v>
       </c>
       <c r="M85">
-        <v>25.45321160000001</v>
+        <v>25.75987680000001</v>
       </c>
       <c r="N85">
-        <v>-2.228211600000009</v>
+        <v>-2.53487680000001</v>
       </c>
       <c r="O85">
-        <v>-0.512488668000002</v>
+        <v>-0.5830216640000023</v>
       </c>
       <c r="P85">
-        <v>-1.715722932000007</v>
+        <v>-1.951855136000008</v>
       </c>
       <c r="Q85">
-        <v>2.184277067999992</v>
+        <v>1.948144863999991</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3450554825564064</v>
+        <v>0.3637589502161819</v>
       </c>
       <c r="T85">
-        <v>4.629387140499388</v>
+        <v>4.918723836780601</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.2098654615357065</v>
+        <v>0.2073670631840909</v>
       </c>
       <c r="W85">
-        <v>0.1159917502465583</v>
+        <v>0.1163585151245755</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.9124585284161152</v>
+        <v>0.9015959268873518</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8285,22 +8285,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1559425847392324</v>
+        <v>0.1569525847392325</v>
       </c>
       <c r="C86">
-        <v>-58.40387744862186</v>
+        <v>-61.5085170749837</v>
       </c>
       <c r="D86">
-        <v>115.8821225513781</v>
+        <v>114.8664829250163</v>
       </c>
       <c r="E86">
-        <v>50.276</v>
+        <v>52.36499999999999</v>
       </c>
       <c r="F86">
-        <v>175.476</v>
+        <v>177.565</v>
       </c>
       <c r="G86">
         <v>1.19</v>
@@ -8321,37 +8321,37 @@
         <v>23.225</v>
       </c>
       <c r="M86">
-        <v>25.7598768</v>
+        <v>26.066542</v>
       </c>
       <c r="N86">
-        <v>-2.534876800000003</v>
+        <v>-2.841542000000004</v>
       </c>
       <c r="O86">
-        <v>-0.5830216640000007</v>
+        <v>-0.653554660000001</v>
       </c>
       <c r="P86">
-        <v>-1.951855136000002</v>
+        <v>-2.187987340000003</v>
       </c>
       <c r="Q86">
-        <v>1.948144863999997</v>
+        <v>1.712012659999996</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3637589502161816</v>
+        <v>0.3849562135639271</v>
       </c>
       <c r="T86">
-        <v>4.918723836780597</v>
+        <v>5.246638759232638</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.207367063184091</v>
+        <v>0.2049274506760428</v>
       </c>
       <c r="W86">
-        <v>0.1163585151245754</v>
+        <v>0.1167166502407569</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.9015959268873521</v>
+        <v>0.8909889159827949</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8367,22 +8367,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1569525847392325</v>
+        <v>0.1579625847392325</v>
       </c>
       <c r="C87">
-        <v>-61.5085170749837</v>
+        <v>-64.59550839343238</v>
       </c>
       <c r="D87">
-        <v>114.8664829250163</v>
+        <v>113.8684916065676</v>
       </c>
       <c r="E87">
-        <v>52.36499999999999</v>
+        <v>54.45399999999999</v>
       </c>
       <c r="F87">
-        <v>177.565</v>
+        <v>179.654</v>
       </c>
       <c r="G87">
         <v>1.19</v>
@@ -8403,37 +8403,37 @@
         <v>23.225</v>
       </c>
       <c r="M87">
-        <v>26.066542</v>
+        <v>26.3732072</v>
       </c>
       <c r="N87">
-        <v>-2.841542000000004</v>
+        <v>-3.148207200000005</v>
       </c>
       <c r="O87">
-        <v>-0.653554660000001</v>
+        <v>-0.7240876560000012</v>
       </c>
       <c r="P87">
-        <v>-2.187987340000003</v>
+        <v>-2.424119544000004</v>
       </c>
       <c r="Q87">
-        <v>1.712012659999996</v>
+        <v>1.475880455999995</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3849562135639271</v>
+        <v>0.4091816573899219</v>
       </c>
       <c r="T87">
-        <v>5.246638759232638</v>
+        <v>5.621398670606397</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2049274506760428</v>
+        <v>0.2025445733426005</v>
       </c>
       <c r="W87">
-        <v>0.1167166502407569</v>
+        <v>0.1170664566333063</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8909889159827949</v>
+        <v>0.8806285797504368</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8449,22 +8449,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1579625847392325</v>
+        <v>0.1589725847392324</v>
       </c>
       <c r="C88">
-        <v>-64.59550839343238</v>
+        <v>-67.66530744171877</v>
       </c>
       <c r="D88">
-        <v>113.8684916065676</v>
+        <v>112.8876925582812</v>
       </c>
       <c r="E88">
-        <v>54.45399999999999</v>
+        <v>56.54299999999999</v>
       </c>
       <c r="F88">
-        <v>179.654</v>
+        <v>181.743</v>
       </c>
       <c r="G88">
         <v>1.19</v>
@@ -8485,37 +8485,37 @@
         <v>23.225</v>
       </c>
       <c r="M88">
-        <v>26.3732072</v>
+        <v>26.6798724</v>
       </c>
       <c r="N88">
-        <v>-3.148207200000005</v>
+        <v>-3.454872400000003</v>
       </c>
       <c r="O88">
-        <v>-0.7240876560000012</v>
+        <v>-0.7946206520000006</v>
       </c>
       <c r="P88">
-        <v>-2.424119544000004</v>
+        <v>-2.660251748000002</v>
       </c>
       <c r="Q88">
-        <v>1.475880455999995</v>
+        <v>1.239748251999996</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4091816573899219</v>
+        <v>0.437134092573762</v>
       </c>
       <c r="T88">
-        <v>5.621398670606397</v>
+        <v>6.053813952960735</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.2025445733426005</v>
+        <v>0.2002164747984327</v>
       </c>
       <c r="W88">
-        <v>0.1170664566333063</v>
+        <v>0.1174082214995901</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8806285797504368</v>
+        <v>0.8705064121670986</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8531,22 +8531,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1589725847392324</v>
+        <v>0.1599825847392325</v>
       </c>
       <c r="C89">
-        <v>-67.66530744171877</v>
+        <v>-70.71835467956505</v>
       </c>
       <c r="D89">
-        <v>112.8876925582812</v>
+        <v>111.9236453204349</v>
       </c>
       <c r="E89">
-        <v>56.54299999999999</v>
+        <v>58.63199999999999</v>
       </c>
       <c r="F89">
-        <v>181.743</v>
+        <v>183.832</v>
       </c>
       <c r="G89">
         <v>1.19</v>
@@ -8567,37 +8567,37 @@
         <v>23.225</v>
       </c>
       <c r="M89">
-        <v>26.6798724</v>
+        <v>26.9865376</v>
       </c>
       <c r="N89">
-        <v>-3.454872400000003</v>
+        <v>-3.761537600000004</v>
       </c>
       <c r="O89">
-        <v>-0.7946206520000006</v>
+        <v>-0.8651536480000009</v>
       </c>
       <c r="P89">
-        <v>-2.660251748000002</v>
+        <v>-2.896383952000003</v>
       </c>
       <c r="Q89">
-        <v>1.239748251999996</v>
+        <v>1.003616047999996</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.437134092573762</v>
+        <v>0.4697452669549089</v>
       </c>
       <c r="T89">
-        <v>6.053813952960735</v>
+        <v>6.558298449040797</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.2002164747984327</v>
+        <v>0.1979412875848141</v>
       </c>
       <c r="W89">
-        <v>0.1174082214995901</v>
+        <v>0.1177422189825493</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8705064121670986</v>
+        <v>0.8606142938470178</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8613,22 +8613,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1599825847392325</v>
+        <v>0.1609925847392325</v>
       </c>
       <c r="C90">
-        <v>-70.71835467956505</v>
+        <v>-73.75507564820433</v>
       </c>
       <c r="D90">
-        <v>111.9236453204349</v>
+        <v>110.9759243517957</v>
       </c>
       <c r="E90">
-        <v>58.63199999999999</v>
+        <v>60.72100000000002</v>
       </c>
       <c r="F90">
-        <v>183.832</v>
+        <v>185.921</v>
       </c>
       <c r="G90">
         <v>1.19</v>
@@ -8649,37 +8649,37 @@
         <v>23.225</v>
       </c>
       <c r="M90">
-        <v>26.9865376</v>
+        <v>27.29320280000001</v>
       </c>
       <c r="N90">
-        <v>-3.761537600000004</v>
+        <v>-4.068202800000009</v>
       </c>
       <c r="O90">
-        <v>-0.8651536480000009</v>
+        <v>-0.935686644000002</v>
       </c>
       <c r="P90">
-        <v>-2.896383952000003</v>
+        <v>-3.132516156000007</v>
       </c>
       <c r="Q90">
-        <v>1.003616047999996</v>
+        <v>0.767483843999992</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4697452669549089</v>
+        <v>0.5082857457689917</v>
       </c>
       <c r="T90">
-        <v>6.558298449040797</v>
+        <v>7.154507398953599</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.1979412875848141</v>
+        <v>0.1957172281737488</v>
       </c>
       <c r="W90">
-        <v>0.1177422189825493</v>
+        <v>0.1180687109040937</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8606142938470178</v>
+        <v>0.8509444703206468</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8695,22 +8695,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1609925847392325</v>
+        <v>0.1620025847392325</v>
       </c>
       <c r="C91">
-        <v>-73.75507564820433</v>
+        <v>-76.77588159669403</v>
       </c>
       <c r="D91">
-        <v>110.9759243517957</v>
+        <v>110.044118403306</v>
       </c>
       <c r="E91">
-        <v>60.72100000000002</v>
+        <v>62.81000000000002</v>
       </c>
       <c r="F91">
-        <v>185.921</v>
+        <v>188.01</v>
       </c>
       <c r="G91">
         <v>1.19</v>
@@ -8731,37 +8731,37 @@
         <v>23.225</v>
       </c>
       <c r="M91">
-        <v>27.29320280000001</v>
+        <v>27.599868</v>
       </c>
       <c r="N91">
-        <v>-4.068202800000009</v>
+        <v>-4.374868000000006</v>
       </c>
       <c r="O91">
-        <v>-0.935686644000002</v>
+        <v>-1.006219640000001</v>
       </c>
       <c r="P91">
-        <v>-3.132516156000007</v>
+        <v>-3.368648360000005</v>
       </c>
       <c r="Q91">
-        <v>0.767483843999992</v>
+        <v>0.5313516399999934</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5082857457689917</v>
+        <v>0.5545343203458907</v>
       </c>
       <c r="T91">
-        <v>7.154507398953599</v>
+        <v>7.869958138848958</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.1957172281737488</v>
+        <v>0.1935425923051516</v>
       </c>
       <c r="W91">
-        <v>0.1180687109040937</v>
+        <v>0.1183879474496038</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8509444703206468</v>
+        <v>0.8414895317615285</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8777,22 +8777,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1620025847392325</v>
+        <v>0.1630125847392324</v>
       </c>
       <c r="C92">
-        <v>-76.77588159669403</v>
+        <v>-79.78117007693893</v>
       </c>
       <c r="D92">
-        <v>110.044118403306</v>
+        <v>109.1278299230611</v>
       </c>
       <c r="E92">
-        <v>62.81000000000002</v>
+        <v>64.89900000000002</v>
       </c>
       <c r="F92">
-        <v>188.01</v>
+        <v>190.099</v>
       </c>
       <c r="G92">
         <v>1.19</v>
@@ -8813,37 +8813,37 @@
         <v>23.225</v>
       </c>
       <c r="M92">
-        <v>27.599868</v>
+        <v>27.90653320000001</v>
       </c>
       <c r="N92">
-        <v>-4.374868000000006</v>
+        <v>-4.681533200000008</v>
       </c>
       <c r="O92">
-        <v>-1.006219640000001</v>
+        <v>-1.076752636000002</v>
       </c>
       <c r="P92">
-        <v>-3.368648360000005</v>
+        <v>-3.604780564000006</v>
       </c>
       <c r="Q92">
-        <v>0.5313516399999934</v>
+        <v>0.2952194359999929</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5545343203458907</v>
+        <v>0.6110603559398785</v>
       </c>
       <c r="T92">
-        <v>7.869958138848958</v>
+        <v>8.744397932054397</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.1935425923051516</v>
+        <v>0.1914157506314686</v>
       </c>
       <c r="W92">
-        <v>0.1183879474496038</v>
+        <v>0.1187001678073004</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8414895317615285</v>
+        <v>0.8322423940498633</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8859,22 +8859,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1630125847392324</v>
+        <v>0.1640225847392325</v>
       </c>
       <c r="C93">
-        <v>-79.78117007693893</v>
+        <v>-82.77132550923261</v>
       </c>
       <c r="D93">
-        <v>109.1278299230611</v>
+        <v>108.2266744907674</v>
       </c>
       <c r="E93">
-        <v>64.89900000000002</v>
+        <v>66.98800000000001</v>
       </c>
       <c r="F93">
-        <v>190.099</v>
+        <v>192.188</v>
       </c>
       <c r="G93">
         <v>1.19</v>
@@ -8895,37 +8895,37 @@
         <v>23.225</v>
       </c>
       <c r="M93">
-        <v>27.90653320000001</v>
+        <v>28.21319840000001</v>
       </c>
       <c r="N93">
-        <v>-4.681533200000008</v>
+        <v>-4.988198400000009</v>
       </c>
       <c r="O93">
-        <v>-1.076752636000002</v>
+        <v>-1.147285632000002</v>
       </c>
       <c r="P93">
-        <v>-3.604780564000006</v>
+        <v>-3.840912768000007</v>
       </c>
       <c r="Q93">
-        <v>0.2952194359999929</v>
+        <v>0.05908723199999155</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6110603559398785</v>
+        <v>0.6817179004323636</v>
       </c>
       <c r="T93">
-        <v>8.744397932054397</v>
+        <v>9.837447673561201</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.1914157506314686</v>
+        <v>0.1893351446463439</v>
       </c>
       <c r="W93">
-        <v>0.1187001678073004</v>
+        <v>0.1190056007659167</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8322423940498633</v>
+        <v>0.8231962810710605</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8941,22 +8941,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1640225847392325</v>
+        <v>0.1650325847392325</v>
       </c>
       <c r="C94">
-        <v>-82.77132550923261</v>
+        <v>-85.74671972000762</v>
       </c>
       <c r="D94">
-        <v>108.2266744907674</v>
+        <v>107.3402802799924</v>
       </c>
       <c r="E94">
-        <v>66.98800000000001</v>
+        <v>69.07700000000001</v>
       </c>
       <c r="F94">
-        <v>192.188</v>
+        <v>194.277</v>
       </c>
       <c r="G94">
         <v>1.19</v>
@@ -8977,37 +8977,37 @@
         <v>23.225</v>
       </c>
       <c r="M94">
-        <v>28.21319840000001</v>
+        <v>28.5198636</v>
       </c>
       <c r="N94">
-        <v>-4.988198400000009</v>
+        <v>-5.294863600000006</v>
       </c>
       <c r="O94">
-        <v>-1.147285632000002</v>
+        <v>-1.217818628000002</v>
       </c>
       <c r="P94">
-        <v>-3.840912768000007</v>
+        <v>-4.077044972000005</v>
       </c>
       <c r="Q94">
-        <v>0.05908723199999155</v>
+        <v>-0.1770449720000062</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6817179004323636</v>
+        <v>0.7725633147798443</v>
       </c>
       <c r="T94">
-        <v>9.837447673561201</v>
+        <v>11.2427973412128</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.1893351446463439</v>
+        <v>0.1872992828759531</v>
       </c>
       <c r="W94">
-        <v>0.1190056007659167</v>
+        <v>0.1193044652738101</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8231962810710605</v>
+        <v>0.8143447081563179</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9023,22 +9023,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1650325847392325</v>
+        <v>0.1660425847392324</v>
       </c>
       <c r="C95">
-        <v>-85.74671972000762</v>
+        <v>-88.70771245337488</v>
       </c>
       <c r="D95">
-        <v>107.3402802799924</v>
+        <v>106.4682875466251</v>
       </c>
       <c r="E95">
-        <v>69.07700000000001</v>
+        <v>71.16600000000001</v>
       </c>
       <c r="F95">
-        <v>194.277</v>
+        <v>196.366</v>
       </c>
       <c r="G95">
         <v>1.19</v>
@@ -9059,37 +9059,37 @@
         <v>23.225</v>
       </c>
       <c r="M95">
-        <v>28.5198636</v>
+        <v>28.82652880000001</v>
       </c>
       <c r="N95">
-        <v>-5.294863600000006</v>
+        <v>-5.601528800000008</v>
       </c>
       <c r="O95">
-        <v>-1.217818628000002</v>
+        <v>-1.288351624000002</v>
       </c>
       <c r="P95">
-        <v>-4.077044972000005</v>
+        <v>-4.313177176000005</v>
       </c>
       <c r="Q95">
-        <v>-0.1770449720000062</v>
+        <v>-0.4131771760000067</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7725633147798443</v>
+        <v>0.8936905339098186</v>
       </c>
       <c r="T95">
-        <v>11.2427973412128</v>
+        <v>13.11659689808161</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.1872992828759531</v>
+        <v>0.185306737313443</v>
       </c>
       <c r="W95">
-        <v>0.1193044652738101</v>
+        <v>0.1195969709623866</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8143447081563179</v>
+        <v>0.8056814665801868</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9105,22 +9105,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1660425847392324</v>
+        <v>0.2212383376164565</v>
       </c>
       <c r="C96">
-        <v>-88.70771245337488</v>
+        <v>-123.5309650360301</v>
       </c>
       <c r="D96">
-        <v>106.4682875466251</v>
+        <v>73.73403496396995</v>
       </c>
       <c r="E96">
-        <v>71.16600000000001</v>
+        <v>73.25500000000001</v>
       </c>
       <c r="F96">
-        <v>196.366</v>
+        <v>198.455</v>
       </c>
       <c r="G96">
         <v>1.19</v>
@@ -9141,45 +9141,45 @@
         <v>23.225</v>
       </c>
       <c r="M96">
-        <v>28.82652880000001</v>
+        <v>39.849764</v>
       </c>
       <c r="N96">
-        <v>-5.601528800000008</v>
+        <v>-16.624764</v>
       </c>
       <c r="O96">
-        <v>-1.288351624000002</v>
+        <v>-3.823695720000001</v>
       </c>
       <c r="P96">
-        <v>-4.313177176000005</v>
+        <v>-12.80106828</v>
       </c>
       <c r="Q96">
-        <v>-0.4131771760000067</v>
+        <v>-8.901068280000004</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8936905339098186</v>
+        <v>1.120983698236263</v>
       </c>
       <c r="T96">
-        <v>13.11659689808161</v>
+        <v>16.6327498623232</v>
       </c>
       <c r="U96">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.185306737313443</v>
+        <v>0.1340472179458829</v>
       </c>
       <c r="W96">
-        <v>0.1195969709623866</v>
+        <v>0.1738833186364667</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y96">
-        <v>0.8056814665801868</v>
+        <v>0.5828139910690562</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9187,22 +9187,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2212383376164565</v>
+        <v>0.2227883376164565</v>
       </c>
       <c r="C97">
-        <v>-123.5309650360301</v>
+        <v>-126.2511296273573</v>
       </c>
       <c r="D97">
-        <v>73.73403496396995</v>
+        <v>73.10287037264268</v>
       </c>
       <c r="E97">
-        <v>73.25500000000001</v>
+        <v>75.34400000000001</v>
       </c>
       <c r="F97">
-        <v>198.455</v>
+        <v>200.544</v>
       </c>
       <c r="G97">
         <v>1.19</v>
@@ -9223,37 +9223,37 @@
         <v>23.225</v>
       </c>
       <c r="M97">
-        <v>39.849764</v>
+        <v>40.2692352</v>
       </c>
       <c r="N97">
-        <v>-16.624764</v>
+        <v>-17.04423520000001</v>
       </c>
       <c r="O97">
-        <v>-3.823695720000001</v>
+        <v>-3.920174096000002</v>
       </c>
       <c r="P97">
-        <v>-12.80106828</v>
+        <v>-13.124061104</v>
       </c>
       <c r="Q97">
-        <v>-8.901068280000004</v>
+        <v>-9.224061104000006</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.120983698236263</v>
+        <v>1.38977962279533</v>
       </c>
       <c r="T97">
-        <v>16.6327498623232</v>
+        <v>20.79093732790401</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1340472179458829</v>
+        <v>0.1326508927589466</v>
       </c>
       <c r="W97">
-        <v>0.1738833186364667</v>
+        <v>0.1741637007340035</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5828139910690562</v>
+        <v>0.5767430119954202</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9269,22 +9269,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2227883376164565</v>
+        <v>0.2243383376164565</v>
       </c>
       <c r="C98">
-        <v>-126.2511296273573</v>
+        <v>-128.9605803701713</v>
       </c>
       <c r="D98">
-        <v>73.10287037264268</v>
+        <v>72.48241962982867</v>
       </c>
       <c r="E98">
-        <v>75.34400000000001</v>
+        <v>77.43300000000001</v>
       </c>
       <c r="F98">
-        <v>200.544</v>
+        <v>202.633</v>
       </c>
       <c r="G98">
         <v>1.19</v>
@@ -9305,37 +9305,37 @@
         <v>23.225</v>
       </c>
       <c r="M98">
-        <v>40.2692352</v>
+        <v>40.6887064</v>
       </c>
       <c r="N98">
-        <v>-17.04423520000001</v>
+        <v>-17.4637064</v>
       </c>
       <c r="O98">
-        <v>-3.920174096000002</v>
+        <v>-4.016652472000001</v>
       </c>
       <c r="P98">
-        <v>-13.124061104</v>
+        <v>-13.447053928</v>
       </c>
       <c r="Q98">
-        <v>-9.224061104000006</v>
+        <v>-9.547053928000004</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.389779622795326</v>
+        <v>1.837772830393769</v>
       </c>
       <c r="T98">
-        <v>20.79093732790396</v>
+        <v>27.72124977053861</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1326508927589466</v>
+        <v>0.1312833577820503</v>
       </c>
       <c r="W98">
-        <v>0.1741637007340035</v>
+        <v>0.1744383017573643</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5767430119954202</v>
+        <v>0.5707972077480448</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9351,22 +9351,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2243383376164565</v>
+        <v>0.2258883376164565</v>
       </c>
       <c r="C99">
-        <v>-128.9605803701713</v>
+        <v>-131.6595877656582</v>
       </c>
       <c r="D99">
-        <v>72.48241962982867</v>
+        <v>71.87241223434178</v>
       </c>
       <c r="E99">
-        <v>77.43300000000001</v>
+        <v>79.52200000000001</v>
       </c>
       <c r="F99">
-        <v>202.633</v>
+        <v>204.722</v>
       </c>
       <c r="G99">
         <v>1.19</v>
@@ -9387,37 +9387,37 @@
         <v>23.225</v>
       </c>
       <c r="M99">
-        <v>40.6887064</v>
+        <v>41.1081776</v>
       </c>
       <c r="N99">
-        <v>-17.4637064</v>
+        <v>-17.88317760000001</v>
       </c>
       <c r="O99">
-        <v>-4.016652472000001</v>
+        <v>-4.113130848000002</v>
       </c>
       <c r="P99">
-        <v>-13.447053928</v>
+        <v>-13.77004675200001</v>
       </c>
       <c r="Q99">
-        <v>-9.547053928000004</v>
+        <v>-9.870046752000007</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.837772830393769</v>
+        <v>2.733759245590652</v>
       </c>
       <c r="T99">
-        <v>27.72124977053861</v>
+        <v>41.58187465580792</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1312833577820503</v>
+        <v>0.1299437316822334</v>
       </c>
       <c r="W99">
-        <v>0.1744383017573643</v>
+        <v>0.1747072986782075</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5707972077480448</v>
+        <v>0.5649727464444931</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9433,22 +9433,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2258883376164565</v>
+        <v>0.2274383376164565</v>
       </c>
       <c r="C100">
-        <v>-131.6595877656582</v>
+        <v>-134.3484132849183</v>
       </c>
       <c r="D100">
-        <v>71.87241223434178</v>
+        <v>71.27258671508174</v>
       </c>
       <c r="E100">
-        <v>79.52200000000001</v>
+        <v>81.611</v>
       </c>
       <c r="F100">
-        <v>204.722</v>
+        <v>206.811</v>
       </c>
       <c r="G100">
         <v>1.19</v>
@@ -9469,37 +9469,37 @@
         <v>23.225</v>
       </c>
       <c r="M100">
-        <v>41.1081776</v>
+        <v>41.5276488</v>
       </c>
       <c r="N100">
-        <v>-17.88317760000001</v>
+        <v>-18.3026488</v>
       </c>
       <c r="O100">
-        <v>-4.113130848000002</v>
+        <v>-4.209609224000001</v>
       </c>
       <c r="P100">
-        <v>-13.77004675200001</v>
+        <v>-14.093039576</v>
       </c>
       <c r="Q100">
-        <v>-9.870046752000007</v>
+        <v>-10.193039576</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.733759245590652</v>
+        <v>5.421718491181305</v>
       </c>
       <c r="T100">
-        <v>41.58187465580792</v>
+        <v>83.16374931161583</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1299437316822334</v>
+        <v>0.1286311687359483</v>
       </c>
       <c r="W100">
-        <v>0.1747072986782075</v>
+        <v>0.1749708613178216</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9507,91 +9507,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5649727464444931</v>
+        <v>0.559265951025862</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2274383376164565</v>
-      </c>
-      <c r="C101">
-        <v>-134.3484132849183</v>
-      </c>
-      <c r="D101">
-        <v>71.27258671508174</v>
-      </c>
-      <c r="E101">
-        <v>81.611</v>
-      </c>
-      <c r="F101">
-        <v>206.811</v>
-      </c>
-      <c r="G101">
-        <v>1.19</v>
-      </c>
-      <c r="H101">
-        <v>83.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>27.125</v>
-      </c>
-      <c r="K101">
-        <v>3.899999999999999</v>
-      </c>
-      <c r="L101">
-        <v>23.225</v>
-      </c>
-      <c r="M101">
-        <v>41.5276488</v>
-      </c>
-      <c r="N101">
-        <v>-18.3026488</v>
-      </c>
-      <c r="O101">
-        <v>-4.209609224000001</v>
-      </c>
-      <c r="P101">
-        <v>-14.093039576</v>
-      </c>
-      <c r="Q101">
-        <v>-10.193039576</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.421718491181305</v>
-      </c>
-      <c r="T101">
-        <v>83.16374931161583</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1286311687359483</v>
-      </c>
-      <c r="W101">
-        <v>0.1749708613178216</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.559265951025862</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
